--- a/respiratory/RV_Tracker.xlsx
+++ b/respiratory/RV_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilyjanoff/Desktop/MCPH/Reports/Resp Virus Reports/26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33039559-486A-2243-920D-163B0E2DF733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F92BF8-8F20-6C4A-8318-E310E43E7FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="3620" windowWidth="29440" windowHeight="19780" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8140" yWindow="3040" windowWidth="29440" windowHeight="19780" tabRatio="500" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Flu_Age_Vax" sheetId="9" r:id="rId9"/>
     <sheet name="Highlights" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="136">
   <si>
     <t>Mono County Respiratory Virus Tracker</t>
   </si>
@@ -631,6 +631,9 @@
   <si>
     <t>Moderate</t>
   </si>
+  <si>
+    <t>California is experiencing an early increase in seasonal flu activity, with positive tests, emergency department visits, and hospitalizations exceeding levels seen during September and October in prior seasons. The Bay Area is reporting very high flu test positivity. COVID-19 continues to circulate, although activity is decreasing and illness is less severe than in previous seasons. Staying up to date on recommended respiratory virus immunizations remains important, and CDPH’s Respiratory Virus Hub provides information on prevention, vaccination, testing, and treatment.</t>
+  </si>
 </sst>
 </file>
 
@@ -640,7 +643,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -698,6 +701,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -749,10 +760,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -780,8 +792,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1162,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1200,6 +1215,17 @@
         <v>127</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="18">
+        <v>46308</v>
+      </c>
+      <c r="B4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" t="s">
         <v>128</v>
       </c>
     </row>
@@ -12917,26 +12943,47 @@
       <c r="A203" s="8">
         <v>46300</v>
       </c>
-      <c r="B203" s="6"/>
-      <c r="C203" s="6"/>
-      <c r="D203" s="6"/>
-      <c r="E203" s="6"/>
-      <c r="F203" s="6"/>
-      <c r="G203" s="6"/>
-      <c r="H203" s="6"/>
-      <c r="I203" s="6"/>
-      <c r="J203" s="6"/>
+      <c r="B203" s="6">
+        <v>1</v>
+      </c>
+      <c r="C203" s="6">
+        <v>0</v>
+      </c>
+      <c r="D203" s="6">
+        <v>0</v>
+      </c>
+      <c r="E203" s="6">
+        <v>0</v>
+      </c>
+      <c r="F203" s="6">
+        <v>0</v>
+      </c>
+      <c r="G203" s="6">
+        <v>2</v>
+      </c>
+      <c r="H203" s="6">
+        <v>0</v>
+      </c>
+      <c r="I203" s="6">
+        <v>0</v>
+      </c>
+      <c r="J203" s="6">
+        <v>0</v>
+      </c>
       <c r="K203" s="6"/>
       <c r="L203" s="6"/>
       <c r="M203" s="5" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="N203" s="6"/>
-      <c r="O203" s="6"/>
-      <c r="P203" s="10" t="str">
-        <f t="shared" si="19"/>
-        <v/>
+      <c r="N203" s="6">
+        <v>0</v>
+      </c>
+      <c r="O203" s="6">
+        <v>2</v>
+      </c>
+      <c r="P203" s="10">
+        <v>0</v>
       </c>
       <c r="Q203" s="7"/>
       <c r="R203" s="11">
@@ -17176,23 +17223,35 @@
       <c r="A77" s="8">
         <v>46300</v>
       </c>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="10" t="str">
+      <c r="B77" s="6">
+        <v>1</v>
+      </c>
+      <c r="C77" s="6">
+        <v>6</v>
+      </c>
+      <c r="D77" s="10">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="10" t="str">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="E77" s="6">
+        <v>0</v>
+      </c>
+      <c r="F77" s="6">
+        <v>11</v>
+      </c>
+      <c r="G77" s="10">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="H77" s="6">
+        <v>0</v>
+      </c>
+      <c r="I77" s="6">
+        <v>11</v>
+      </c>
+      <c r="J77" s="10">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K77" s="7"/>
     </row>
@@ -18196,9 +18255,9 @@
         <f>IF(COUNTIFS(Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A9,Weekly_Local!$B:$B,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$B:$B,Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A9))</f>
         <v>2</v>
       </c>
-      <c r="F9" s="5" t="str">
+      <c r="F9" s="5">
         <f>IF(COUNTIFS(Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A9,Weekly_Local!$B:$B,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$B:$B,Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A9))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G9" s="5" t="str">
         <f>IF(AND($A9=53,DATE(YEAR(Config!$B$3),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3),1,4))+1+364&gt;=DATE(YEAR(Config!$B$3)+1,1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+1,1,4))+1),"",TEXT(DATE(YEAR(Config!$B$3)+IF($A9&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A9&gt;=36,0,1),1,4))+1+7*($A9-1)+1,"m/d/yy")&amp;" – "&amp;TEXT(DATE(YEAR(Config!$B$3)+IF($A9&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A9&gt;=36,0,1),1,4))+1+7*($A9-1)+7,"m/d/yy"))</f>
@@ -19760,9 +19819,9 @@
         <f>IF(COUNTIFS(Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A66,Weekly_Local!$C:$C,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$C:$C,Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A66))</f>
         <v>0</v>
       </c>
-      <c r="F66" s="5" t="str">
+      <c r="F66" s="5">
         <f>IF(COUNTIFS(Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A66,Weekly_Local!$C:$C,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$C:$C,Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A66))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G66" s="5" t="str">
         <f>IF(AND($A66=53,DATE(YEAR(Config!$B$3),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3),1,4))+1+364&gt;=DATE(YEAR(Config!$B$3)+1,1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+1,1,4))+1),"",TEXT(DATE(YEAR(Config!$B$3)+IF($A66&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A66&gt;=36,0,1),1,4))+1+7*($A66-1)+1,"m/d/yy")&amp;" – "&amp;TEXT(DATE(YEAR(Config!$B$3)+IF($A66&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A66&gt;=36,0,1),1,4))+1+7*($A66-1)+7,"m/d/yy"))</f>
@@ -21324,9 +21383,9 @@
         <f>IF(COUNTIFS(Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A123,Weekly_Local!$D:$D,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$D:$D,Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A123))</f>
         <v>0</v>
       </c>
-      <c r="F123" s="5" t="str">
+      <c r="F123" s="5">
         <f>IF(COUNTIFS(Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A123,Weekly_Local!$D:$D,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$D:$D,Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A123))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G123" s="5" t="str">
         <f>IF(AND($A123=53,DATE(YEAR(Config!$B$3),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3),1,4))+1+364&gt;=DATE(YEAR(Config!$B$3)+1,1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+1,1,4))+1),"",TEXT(DATE(YEAR(Config!$B$3)+IF($A123&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A123&gt;=36,0,1),1,4))+1+7*($A123-1)+1,"m/d/yy")&amp;" – "&amp;TEXT(DATE(YEAR(Config!$B$3)+IF($A123&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A123&gt;=36,0,1),1,4))+1+7*($A123-1)+7,"m/d/yy"))</f>
@@ -27495,9 +27554,7 @@
       <c r="E5" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="6">
-        <v>0.95</v>
-      </c>
+      <c r="F5" s="6"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
@@ -27507,10 +27564,18 @@
       <c r="A6" s="8">
         <v>46300</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="6"/>
+      <c r="B6" s="15">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="C6" s="15">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="D6" s="15">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="F6" s="6"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
@@ -27994,7 +28059,7 @@
       <c r="J40" s="7"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="A44" s="17" t="s">
         <v>128</v>
       </c>
     </row>
@@ -28005,9 +28070,12 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A44" r:id="rId1" xr:uid="{0C5618FE-1065-7447-A4CF-86B455C694F8}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/respiratory/RV_Tracker.xlsx
+++ b/respiratory/RV_Tracker.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
@@ -622,7 +622,7 @@
     <t xml:space="preserve">Covid-19 test positivity in Mono County fell to 14% (1 of 7 tests), down from 31% the prior week. All 11 flu tests and all 11 RSV tests reported this week were negative.</t>
   </si>
   <si>
-    <t xml:space="preserve">Mammoth Hospital reported 2 flu patients this week, neither a Mono County resident. There were no Covid-19 or RSV patients. Local wastewater sampling has been paused since 9/9 and is expected to resume this week.</t>
+    <t xml:space="preserve">Mammoth Hospital reported 2 flu patients this week, both influenza A and neither a Mono County resident. There were no Covid-19 or RSV patients. Local wastewater sampling has been paused since 9/9 and is expected to resume this week.</t>
   </si>
   <si>
     <t xml:space="preserve">California is seeing an early rise in flu activity. Statewide flu test positivity reached 8.8%, up from 2.9% in early September. Positive tests, emergency department visits, and hospitalizations are above September–October levels in prior seasons, and the Bay Area is reporting very high flu test positivity. Covid-19 activity in California continues to decline, with statewide test positivity at 8.6%.</t>
@@ -13112,11 +13112,15 @@
       <c r="J203" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K203" s="6"/>
-      <c r="L203" s="6"/>
-      <c r="M203" s="5" t="str">
+      <c r="K203" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L203" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" s="5" t="n">
         <f aca="false">IF(AND(K203="",L203=""),"",SUM(K203:L203))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="N203" s="6" t="n">
         <v>0</v>

--- a/respiratory/RV_Tracker.xlsx
+++ b/respiratory/RV_Tracker.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,8 +16,7 @@
     <sheet name="Wastewater_History" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Wastewater_Local" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="State_National" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Flu_Age_Vax" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Highlights" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Highlights" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -186,30 +185,8 @@
 </comments>
 </file>
 
-<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Season-to-date counts. Add a new block of rows for each season; the dashboard shows the current season.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="131">
   <si>
     <t xml:space="preserve">Mono County Respiratory Virus Tracker</t>
   </si>
@@ -232,13 +209,10 @@
     <t xml:space="preserve">4. State_National: optional manual entry from CDPH Respiratory Virus Report and CalCAT. CDC wastewater and NREVSS positivity load live in the dashboard; these cells are the fallback if the live pull fails.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Flu_Age_Vax: season-to-date flu cases by age group and vaccination status.</t>
+    <t xml:space="preserve">5. Highlights: bullets shown on the dashboard Overview; newest first.</t>
   </si>
   <si>
-    <t xml:space="preserve">6. Highlights: bullets shown on the dashboard Overview; newest first.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Config: set the current season label and report date.</t>
+    <t xml:space="preserve">6. Config: set the current season label and report date.</t>
   </si>
   <si>
     <t xml:space="preserve">Conventions</t>
@@ -322,7 +296,7 @@
     <t xml:space="preserve">Wastewater note</t>
   </si>
   <si>
-    <t xml:space="preserve">Wastewater sampling paused after 9/9/2026 (Verily contract ended 9/14/2026); resumes late September 2026 under a new contract.</t>
+    <t xml:space="preserve">Verily sampling resumed 10/21/2026 under a new contract after a gap since 9/9. UC Davis trend classifications are unavailable until more samples are collected.</t>
   </si>
   <si>
     <t xml:space="preserve">Shown on the wastewater panels; clear it when sampling resumes</t>
@@ -395,6 +369,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-27 season starts here (MMWR week 36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-day rule: 2 patients vaccinated &lt;14 days before visit counted as No/Unknown</t>
   </si>
   <si>
     <t xml:space="preserve">Covid positive</t>
@@ -490,6 +467,9 @@
     <t xml:space="preserve">Mammoth Community Water District, Verily (ddPCR). Weekly mean across samples of (target copies/L ÷ PMMoV copies/L) × 1,000,000. Blank = target not assayed that week; 0 = not detected.</t>
   </si>
   <si>
+    <t xml:space="preserve">1 sample (10/21), first under new contract. Influenza A H1 subtype detected at 4.02.</t>
+  </si>
+  <si>
     <t xml:space="preserve">UC Davis trend table (current snapshot)</t>
   </si>
   <si>
@@ -508,16 +488,7 @@
     <t xml:space="preserve">As of</t>
   </si>
   <si>
-    <t xml:space="preserve">No Trend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
+    <t xml:space="preserve">Not available</t>
   </si>
   <si>
     <t xml:space="preserve">H1</t>
@@ -529,10 +500,7 @@
     <t xml:space="preserve">H5</t>
   </si>
   <si>
-    <t xml:space="preserve">Sporadic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overwrite weekly from cricelio.shinyapps.io/Monodashboard. Leave blank until the first 2026-27 update.</t>
+    <t xml:space="preserve">UC Davis dashboard is not updating after the sampling gap; trend classifications return once enough new samples are collected. Overwrite from cricelio.shinyapps.io/Monodashboard when available.</t>
   </si>
   <si>
     <t xml:space="preserve">CA Covid % pos</t>
@@ -563,39 +531,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.cdph.ca.gov/Programs/CID/DCDC/Pages/RespiratoryVirusReport.aspx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vax No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vax Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vax Unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% vaccinated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0–4 yrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5–17 yrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18–49 yrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50–64 yrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65+ yrs</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -629,6 +564,21 @@
   </si>
   <si>
     <t xml:space="preserve">Flu and Covid-19 vaccination is recommended for everyone 6 months and older. CDPH's Respiratory Virus Hub has information on prevention, vaccination, testing, and treatment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mono County reported 1 Covid-19 case, 3 flu cases, and 1 RSV case for the week of 10/19–10/25, down from 6 Covid-19 cases and 7 flu cases the prior week. Season-to-date totals since 9/7 are 25 Covid-19 cases, 11 flu cases, and 2 RSV cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flu test positivity in Mono County was 23% (3 of 13 tests), down from 33% the prior week. Covid-19 test positivity was 10% (1 of 10 tests) and RSV test positivity was 8% (1 of 12 tests).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mammoth Hospital reported 4 flu patients this week (3 influenza A, 1 influenza B); 3 were Mono County residents and 2 of the 4 were vaccinated. There was 1 RSV patient, not a Mono County resident, and no Covid-19 patients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local wastewater sampling resumed on 10/21 after a gap since 9/9. SARS-CoV-2 was detected at a level similar to early September. Influenza A, influenza B, and RSV were not detected, although the influenza A H1 subtype was detected at a low level. UC Davis trend classifications will return once more samples are collected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flu activity in California continues to rise. Statewide flu test positivity reached 11.4%, up from 9.7% the prior week, which is in CDPH's High range. Covid-19 test positivity declined to 6.4%, and RSV test positivity remains very low at 0.6%.</t>
   </si>
 </sst>
 </file>
@@ -1149,30 +1099,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1182,180 +1132,71 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>133</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" display="https://www.cdph.ca.gov/Programs/CID/DCDC/Pages/RespiratoryVirusReport.aspx"/>
-    <hyperlink ref="C8" r:id="rId2" display="https://www.cdph.ca.gov/Programs/CID/DCDC/Pages/Respiratory-Viruses/Home.aspx"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1381,86 +1222,86 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="4" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>46272</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="8" t="n">
-        <v>46280</v>
-      </c>
-      <c r="C4" s="7" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="7" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="C7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1497,70 +1338,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="U1" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="n">
         <v>44893</v>
       </c>
@@ -1607,7 +1448,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
         <v>44900</v>
       </c>
@@ -1654,7 +1495,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
         <v>44907</v>
       </c>
@@ -1701,7 +1542,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>44914</v>
       </c>
@@ -1750,7 +1591,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
         <v>44921</v>
       </c>
@@ -1799,7 +1640,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>44928</v>
       </c>
@@ -1848,7 +1689,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>44935</v>
       </c>
@@ -1897,7 +1738,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>44942</v>
       </c>
@@ -1946,7 +1787,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
         <v>44949</v>
       </c>
@@ -1995,7 +1836,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>44956</v>
       </c>
@@ -2044,7 +1885,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>44963</v>
       </c>
@@ -2093,7 +1934,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>44970</v>
       </c>
@@ -2142,7 +1983,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>44977</v>
       </c>
@@ -2191,7 +2032,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>44984</v>
       </c>
@@ -2240,7 +2081,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>44991</v>
       </c>
@@ -2289,7 +2130,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>44998</v>
       </c>
@@ -2338,7 +2179,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
         <v>45005</v>
       </c>
@@ -2387,7 +2228,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>45012</v>
       </c>
@@ -2436,7 +2277,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
         <v>45019</v>
       </c>
@@ -2485,7 +2326,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
         <v>45026</v>
       </c>
@@ -2534,7 +2375,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
         <v>45033</v>
       </c>
@@ -2583,7 +2424,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
         <v>45040</v>
       </c>
@@ -2632,7 +2473,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
         <v>45047</v>
       </c>
@@ -2681,7 +2522,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
         <v>45054</v>
       </c>
@@ -2730,7 +2571,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
         <v>45061</v>
       </c>
@@ -2779,7 +2620,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>45068</v>
       </c>
@@ -2828,7 +2669,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
         <v>45075</v>
       </c>
@@ -2877,7 +2718,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
         <v>45082</v>
       </c>
@@ -2926,7 +2767,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
         <v>45089</v>
       </c>
@@ -2975,7 +2816,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
         <v>45096</v>
       </c>
@@ -3024,7 +2865,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
         <v>45103</v>
       </c>
@@ -3073,7 +2914,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
         <v>45110</v>
       </c>
@@ -3122,7 +2963,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
         <v>45117</v>
       </c>
@@ -3171,7 +3012,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
         <v>45124</v>
       </c>
@@ -3220,7 +3061,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
         <v>45131</v>
       </c>
@@ -3269,7 +3110,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
         <v>45138</v>
       </c>
@@ -3318,7 +3159,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
         <v>45145</v>
       </c>
@@ -3367,7 +3208,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
         <v>45152</v>
       </c>
@@ -3416,7 +3257,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
         <v>45159</v>
       </c>
@@ -3465,7 +3306,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
         <v>45166</v>
       </c>
@@ -3514,7 +3355,7 @@
         <v>2022-23</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
         <v>45173</v>
       </c>
@@ -3563,7 +3404,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
         <v>45180</v>
       </c>
@@ -3612,7 +3453,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
         <v>45187</v>
       </c>
@@ -3660,7 +3501,7 @@
         <v/>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R44" s="11" t="n">
         <f aca="false">A44+5</f>
@@ -3679,7 +3520,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
         <v>45194</v>
       </c>
@@ -3727,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R45" s="11" t="n">
         <f aca="false">A45+5</f>
@@ -3746,7 +3587,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
         <v>45201</v>
       </c>
@@ -3794,7 +3635,7 @@
         <v/>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R46" s="11" t="n">
         <f aca="false">A46+5</f>
@@ -3813,7 +3654,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
         <v>45208</v>
       </c>
@@ -3861,7 +3702,7 @@
         <v/>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R47" s="11" t="n">
         <f aca="false">A47+5</f>
@@ -3880,7 +3721,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
         <v>45215</v>
       </c>
@@ -3928,7 +3769,7 @@
         <v/>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R48" s="11" t="n">
         <f aca="false">A48+5</f>
@@ -3947,7 +3788,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
         <v>45222</v>
       </c>
@@ -3995,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R49" s="11" t="n">
         <f aca="false">A49+5</f>
@@ -4014,7 +3855,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
         <v>45229</v>
       </c>
@@ -4062,7 +3903,7 @@
         <v/>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R50" s="11" t="n">
         <f aca="false">A50+5</f>
@@ -4081,7 +3922,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
         <v>45236</v>
       </c>
@@ -4129,7 +3970,7 @@
         <v/>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R51" s="11" t="n">
         <f aca="false">A51+5</f>
@@ -4148,7 +3989,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
         <v>45243</v>
       </c>
@@ -4196,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R52" s="11" t="n">
         <f aca="false">A52+5</f>
@@ -4215,7 +4056,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
         <v>45250</v>
       </c>
@@ -4263,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R53" s="11" t="n">
         <f aca="false">A53+5</f>
@@ -4282,7 +4123,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
         <v>45257</v>
       </c>
@@ -4330,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R54" s="11" t="n">
         <f aca="false">A54+5</f>
@@ -4349,7 +4190,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
         <v>45264</v>
       </c>
@@ -4397,7 +4238,7 @@
         <v/>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R55" s="11" t="n">
         <f aca="false">A55+5</f>
@@ -4416,7 +4257,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
         <v>45271</v>
       </c>
@@ -4464,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R56" s="11" t="n">
         <f aca="false">A56+5</f>
@@ -4483,7 +4324,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
         <v>45278</v>
       </c>
@@ -4531,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R57" s="11" t="n">
         <f aca="false">A57+5</f>
@@ -4550,7 +4391,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
         <v>45285</v>
       </c>
@@ -4598,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R58" s="11" t="n">
         <f aca="false">A58+5</f>
@@ -4617,7 +4458,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
         <v>45292</v>
       </c>
@@ -4665,7 +4506,7 @@
         <v>0</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R59" s="11" t="n">
         <f aca="false">A59+5</f>
@@ -4684,7 +4525,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
         <v>45299</v>
       </c>
@@ -4732,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R60" s="11" t="n">
         <f aca="false">A60+5</f>
@@ -4751,7 +4592,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
         <v>45306</v>
       </c>
@@ -4799,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R61" s="11" t="n">
         <f aca="false">A61+5</f>
@@ -4818,7 +4659,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
         <v>45313</v>
       </c>
@@ -4866,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R62" s="11" t="n">
         <f aca="false">A62+5</f>
@@ -4885,7 +4726,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
         <v>45320</v>
       </c>
@@ -4933,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R63" s="11" t="n">
         <f aca="false">A63+5</f>
@@ -4952,7 +4793,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
         <v>45327</v>
       </c>
@@ -5000,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R64" s="11" t="n">
         <f aca="false">A64+5</f>
@@ -5019,7 +4860,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
         <v>45334</v>
       </c>
@@ -5067,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R65" s="11" t="n">
         <f aca="false">A65+5</f>
@@ -5086,7 +4927,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
         <v>45341</v>
       </c>
@@ -5134,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R66" s="11" t="n">
         <f aca="false">A66+5</f>
@@ -5153,7 +4994,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
         <v>45348</v>
       </c>
@@ -5201,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R67" s="11" t="n">
         <f aca="false">A67+5</f>
@@ -5220,7 +5061,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
         <v>45355</v>
       </c>
@@ -5268,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R68" s="11" t="n">
         <f aca="false">A68+5</f>
@@ -5287,7 +5128,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
         <v>45362</v>
       </c>
@@ -5335,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R69" s="11" t="n">
         <f aca="false">A69+5</f>
@@ -5354,7 +5195,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
         <v>45369</v>
       </c>
@@ -5402,7 +5243,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R70" s="11" t="n">
         <f aca="false">A70+5</f>
@@ -5421,7 +5262,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
         <v>45376</v>
       </c>
@@ -5469,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R71" s="11" t="n">
         <f aca="false">A71+5</f>
@@ -5488,7 +5329,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
         <v>45383</v>
       </c>
@@ -5537,7 +5378,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
         <v>45390</v>
       </c>
@@ -5586,7 +5427,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
         <v>45397</v>
       </c>
@@ -5635,7 +5476,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
         <v>45404</v>
       </c>
@@ -5684,7 +5525,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
         <v>45411</v>
       </c>
@@ -5733,7 +5574,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
         <v>45418</v>
       </c>
@@ -5782,7 +5623,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
         <v>45425</v>
       </c>
@@ -5831,7 +5672,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
         <v>45432</v>
       </c>
@@ -5880,7 +5721,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
         <v>45439</v>
       </c>
@@ -5929,7 +5770,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
         <v>45446</v>
       </c>
@@ -5978,7 +5819,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
         <v>45453</v>
       </c>
@@ -6027,7 +5868,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
         <v>45460</v>
       </c>
@@ -6076,7 +5917,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="n">
         <v>45467</v>
       </c>
@@ -6125,7 +5966,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="n">
         <v>45474</v>
       </c>
@@ -6174,7 +6015,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="n">
         <v>45481</v>
       </c>
@@ -6223,7 +6064,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="n">
         <v>45488</v>
       </c>
@@ -6272,7 +6113,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="n">
         <v>45495</v>
       </c>
@@ -6321,7 +6162,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="n">
         <v>45502</v>
       </c>
@@ -6370,7 +6211,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="n">
         <v>45509</v>
       </c>
@@ -6419,7 +6260,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="n">
         <v>45516</v>
       </c>
@@ -6468,7 +6309,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="n">
         <v>45523</v>
       </c>
@@ -6517,7 +6358,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="n">
         <v>45530</v>
       </c>
@@ -6566,7 +6407,7 @@
         <v>2023-24</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="n">
         <v>45537</v>
       </c>
@@ -6615,7 +6456,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="n">
         <v>45544</v>
       </c>
@@ -6664,7 +6505,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="n">
         <v>45551</v>
       </c>
@@ -6713,7 +6554,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="n">
         <v>45558</v>
       </c>
@@ -6765,7 +6606,7 @@
         <v>0</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R97" s="11" t="n">
         <f aca="false">A97+5</f>
@@ -6784,7 +6625,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="n">
         <v>45565</v>
       </c>
@@ -6836,7 +6677,7 @@
         <v/>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R98" s="11" t="n">
         <f aca="false">A98+5</f>
@@ -6855,7 +6696,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="n">
         <v>45572</v>
       </c>
@@ -6907,7 +6748,7 @@
         <v/>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R99" s="11" t="n">
         <f aca="false">A99+5</f>
@@ -6926,7 +6767,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="n">
         <v>45579</v>
       </c>
@@ -6978,7 +6819,7 @@
         <v/>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R100" s="11" t="n">
         <f aca="false">A100+5</f>
@@ -6997,7 +6838,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="n">
         <v>45586</v>
       </c>
@@ -7049,7 +6890,7 @@
         <v/>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R101" s="11" t="n">
         <f aca="false">A101+5</f>
@@ -7068,7 +6909,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="n">
         <v>45593</v>
       </c>
@@ -7120,7 +6961,7 @@
         <v/>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R102" s="11" t="n">
         <f aca="false">A102+5</f>
@@ -7139,7 +6980,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="n">
         <v>45600</v>
       </c>
@@ -7191,7 +7032,7 @@
         <v/>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R103" s="11" t="n">
         <f aca="false">A103+5</f>
@@ -7210,7 +7051,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="n">
         <v>45607</v>
       </c>
@@ -7262,7 +7103,7 @@
         <v/>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R104" s="11" t="n">
         <f aca="false">A104+5</f>
@@ -7281,7 +7122,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="n">
         <v>45614</v>
       </c>
@@ -7333,7 +7174,7 @@
         <v/>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R105" s="11" t="n">
         <f aca="false">A105+5</f>
@@ -7352,7 +7193,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="8" t="n">
         <v>45621</v>
       </c>
@@ -7404,7 +7245,7 @@
         <v>0</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R106" s="11" t="n">
         <f aca="false">A106+5</f>
@@ -7423,7 +7264,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="n">
         <v>45628</v>
       </c>
@@ -7475,7 +7316,7 @@
         <v>0.5</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R107" s="11" t="n">
         <f aca="false">A107+5</f>
@@ -7494,7 +7335,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="n">
         <v>45635</v>
       </c>
@@ -7546,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R108" s="11" t="n">
         <f aca="false">A108+5</f>
@@ -7565,7 +7406,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="n">
         <v>45642</v>
       </c>
@@ -7617,7 +7458,7 @@
         <v>0.176470588235294</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R109" s="11" t="n">
         <f aca="false">A109+5</f>
@@ -7636,7 +7477,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="n">
         <v>45649</v>
       </c>
@@ -7688,7 +7529,7 @@
         <v>0.0416666666666667</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R110" s="11" t="n">
         <f aca="false">A110+5</f>
@@ -7707,7 +7548,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="n">
         <v>45656</v>
       </c>
@@ -7759,7 +7600,7 @@
         <v>0.0810810810810811</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R111" s="11" t="n">
         <f aca="false">A111+5</f>
@@ -7778,7 +7619,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="8" t="n">
         <v>45663</v>
       </c>
@@ -7830,7 +7671,7 @@
         <v>0.25</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R112" s="11" t="n">
         <f aca="false">A112+5</f>
@@ -7849,7 +7690,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="8" t="n">
         <v>45670</v>
       </c>
@@ -7901,7 +7742,7 @@
         <v>0</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R113" s="11" t="n">
         <f aca="false">A113+5</f>
@@ -7920,7 +7761,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="n">
         <v>45677</v>
       </c>
@@ -7972,7 +7813,7 @@
         <v>0.0666666666666667</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R114" s="11" t="n">
         <f aca="false">A114+5</f>
@@ -7991,7 +7832,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="n">
         <v>45684</v>
       </c>
@@ -8043,7 +7884,7 @@
         <v>0.291666666666667</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R115" s="11" t="n">
         <f aca="false">A115+5</f>
@@ -8062,7 +7903,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="n">
         <v>45691</v>
       </c>
@@ -8114,7 +7955,7 @@
         <v>0.269230769230769</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R116" s="11" t="n">
         <f aca="false">A116+5</f>
@@ -8133,7 +7974,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="8" t="n">
         <v>45698</v>
       </c>
@@ -8185,7 +8026,7 @@
         <v>0.3</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R117" s="11" t="n">
         <f aca="false">A117+5</f>
@@ -8204,7 +8045,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="8" t="n">
         <v>45705</v>
       </c>
@@ -8256,7 +8097,7 @@
         <v>0.222222222222222</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R118" s="11" t="n">
         <f aca="false">A118+5</f>
@@ -8275,7 +8116,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="8" t="n">
         <v>45712</v>
       </c>
@@ -8327,7 +8168,7 @@
         <v>0.25</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R119" s="11" t="n">
         <f aca="false">A119+5</f>
@@ -8346,7 +8187,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="8" t="n">
         <v>45719</v>
       </c>
@@ -8398,7 +8239,7 @@
         <v>0.25</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R120" s="11" t="n">
         <f aca="false">A120+5</f>
@@ -8417,7 +8258,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="n">
         <v>45726</v>
       </c>
@@ -8469,7 +8310,7 @@
         <v>0.2</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R121" s="11" t="n">
         <f aca="false">A121+5</f>
@@ -8488,7 +8329,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="8" t="n">
         <v>45733</v>
       </c>
@@ -8540,7 +8381,7 @@
         <v>0.333333333333333</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R122" s="11" t="n">
         <f aca="false">A122+5</f>
@@ -8559,7 +8400,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="8" t="n">
         <v>45740</v>
       </c>
@@ -8611,7 +8452,7 @@
         <v>0.2</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R123" s="11" t="n">
         <f aca="false">A123+5</f>
@@ -8630,7 +8471,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="8" t="n">
         <v>45747</v>
       </c>
@@ -8679,7 +8520,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="8" t="n">
         <v>45754</v>
       </c>
@@ -8728,7 +8569,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="8" t="n">
         <v>45761</v>
       </c>
@@ -8777,7 +8618,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="8" t="n">
         <v>45768</v>
       </c>
@@ -8826,7 +8667,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="8" t="n">
         <v>45775</v>
       </c>
@@ -8875,7 +8716,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="8" t="n">
         <v>45782</v>
       </c>
@@ -8924,7 +8765,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="8" t="n">
         <v>45789</v>
       </c>
@@ -8973,7 +8814,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="8" t="n">
         <v>45796</v>
       </c>
@@ -9022,7 +8863,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="8" t="n">
         <v>45803</v>
       </c>
@@ -9071,7 +8912,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="8" t="n">
         <v>45810</v>
       </c>
@@ -9120,7 +8961,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="8" t="n">
         <v>45817</v>
       </c>
@@ -9169,7 +9010,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="8" t="n">
         <v>45824</v>
       </c>
@@ -9218,7 +9059,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="8" t="n">
         <v>45831</v>
       </c>
@@ -9267,7 +9108,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="8" t="n">
         <v>45838</v>
       </c>
@@ -9316,7 +9157,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="8" t="n">
         <v>45845</v>
       </c>
@@ -9365,7 +9206,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="8" t="n">
         <v>45852</v>
       </c>
@@ -9414,7 +9255,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="8" t="n">
         <v>45859</v>
       </c>
@@ -9463,7 +9304,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="8" t="n">
         <v>45866</v>
       </c>
@@ -9512,7 +9353,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="8" t="n">
         <v>45873</v>
       </c>
@@ -9561,7 +9402,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="8" t="n">
         <v>45880</v>
       </c>
@@ -9610,7 +9451,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="8" t="n">
         <v>45887</v>
       </c>
@@ -9659,7 +9500,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="8" t="n">
         <v>45894</v>
       </c>
@@ -9708,7 +9549,7 @@
         <v>2024-25</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="8" t="n">
         <v>45901</v>
       </c>
@@ -9757,7 +9598,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="8" t="n">
         <v>45908</v>
       </c>
@@ -9806,7 +9647,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="8" t="n">
         <v>45915</v>
       </c>
@@ -9855,7 +9696,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="8" t="n">
         <v>45922</v>
       </c>
@@ -9924,7 +9765,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="8" t="n">
         <v>45929</v>
       </c>
@@ -9993,7 +9834,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="8" t="n">
         <v>45936</v>
       </c>
@@ -10062,7 +9903,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="8" t="n">
         <v>45943</v>
       </c>
@@ -10131,7 +9972,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="8" t="n">
         <v>45950</v>
       </c>
@@ -10200,7 +10041,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="8" t="n">
         <v>45957</v>
       </c>
@@ -10269,7 +10110,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="8" t="n">
         <v>45964</v>
       </c>
@@ -10338,7 +10179,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="8" t="n">
         <v>45971</v>
       </c>
@@ -10407,7 +10248,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="8" t="n">
         <v>45978</v>
       </c>
@@ -10476,7 +10317,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="8" t="n">
         <v>45985</v>
       </c>
@@ -10545,7 +10386,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="8" t="n">
         <v>45992</v>
       </c>
@@ -10614,7 +10455,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="8" t="n">
         <v>45999</v>
       </c>
@@ -10683,7 +10524,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="8" t="n">
         <v>46006</v>
       </c>
@@ -10752,7 +10593,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="8" t="n">
         <v>46013</v>
       </c>
@@ -10821,7 +10662,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="8" t="n">
         <v>46020</v>
       </c>
@@ -10890,7 +10731,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="8" t="n">
         <v>46027</v>
       </c>
@@ -10959,7 +10800,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="8" t="n">
         <v>46034</v>
       </c>
@@ -11028,7 +10869,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="8" t="n">
         <v>46041</v>
       </c>
@@ -11097,7 +10938,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="8" t="n">
         <v>46048</v>
       </c>
@@ -11166,7 +11007,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="8" t="n">
         <v>46055</v>
       </c>
@@ -11235,7 +11076,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="8" t="n">
         <v>46062</v>
       </c>
@@ -11304,7 +11145,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="8" t="n">
         <v>46069</v>
       </c>
@@ -11373,7 +11214,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="8" t="n">
         <v>46076</v>
       </c>
@@ -11442,7 +11283,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="8" t="n">
         <v>46083</v>
       </c>
@@ -11511,7 +11352,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="8" t="n">
         <v>46090</v>
       </c>
@@ -11580,7 +11421,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="8" t="n">
         <v>46097</v>
       </c>
@@ -11649,7 +11490,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="8" t="n">
         <v>46104</v>
       </c>
@@ -11718,7 +11559,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="8" t="n">
         <v>46111</v>
       </c>
@@ -11767,7 +11608,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="8" t="n">
         <v>46118</v>
       </c>
@@ -11816,7 +11657,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="8" t="n">
         <v>46125</v>
       </c>
@@ -11865,7 +11706,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="8" t="n">
         <v>46132</v>
       </c>
@@ -11914,7 +11755,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="8" t="n">
         <v>46139</v>
       </c>
@@ -11963,7 +11804,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="8" t="n">
         <v>46146</v>
       </c>
@@ -12012,7 +11853,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="8" t="n">
         <v>46153</v>
       </c>
@@ -12061,7 +11902,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="8" t="n">
         <v>46160</v>
       </c>
@@ -12110,7 +11951,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="8" t="n">
         <v>46167</v>
       </c>
@@ -12159,7 +12000,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="8" t="n">
         <v>46174</v>
       </c>
@@ -12208,7 +12049,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="8" t="n">
         <v>46181</v>
       </c>
@@ -12257,7 +12098,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="8" t="n">
         <v>46188</v>
       </c>
@@ -12306,7 +12147,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="8" t="n">
         <v>46195</v>
       </c>
@@ -12355,7 +12196,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="8" t="n">
         <v>46202</v>
       </c>
@@ -12404,7 +12245,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="8" t="n">
         <v>46209</v>
       </c>
@@ -12453,7 +12294,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="8" t="n">
         <v>46216</v>
       </c>
@@ -12502,7 +12343,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="8" t="n">
         <v>46223</v>
       </c>
@@ -12551,7 +12392,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="8" t="n">
         <v>46230</v>
       </c>
@@ -12600,7 +12441,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="8" t="n">
         <v>46237</v>
       </c>
@@ -12649,7 +12490,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="8" t="n">
         <v>46244</v>
       </c>
@@ -12698,7 +12539,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="8" t="n">
         <v>46251</v>
       </c>
@@ -12747,7 +12588,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="8" t="n">
         <v>46258</v>
       </c>
@@ -12796,7 +12637,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="8" t="n">
         <v>46265</v>
       </c>
@@ -12845,7 +12686,7 @@
         <v>2025-26</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="8" t="n">
         <v>46272</v>
       </c>
@@ -12877,7 +12718,7 @@
         <v/>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R199" s="11" t="n">
         <f aca="false">A199+5</f>
@@ -12896,7 +12737,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="8" t="n">
         <v>46279</v>
       </c>
@@ -12945,7 +12786,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="8" t="n">
         <v>46286</v>
       </c>
@@ -12992,8 +12833,9 @@
       <c r="O201" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P201" s="10" t="n">
-        <v>0</v>
+      <c r="P201" s="10" t="str">
+        <f aca="false">IF(OR(M201="",M201=0),"",IF(N201="",0,N201)/M201)</f>
+        <v/>
       </c>
       <c r="Q201" s="7"/>
       <c r="R201" s="11" t="n">
@@ -13013,7 +12855,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="8" t="n">
         <v>46293</v>
       </c>
@@ -13060,8 +12902,9 @@
       <c r="O202" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P202" s="10" t="n">
-        <v>0</v>
+      <c r="P202" s="10" t="str">
+        <f aca="false">IF(OR(M202="",M202=0),"",IF(N202="",0,N202)/M202)</f>
+        <v/>
       </c>
       <c r="Q202" s="7"/>
       <c r="R202" s="11" t="n">
@@ -13081,7 +12924,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="8" t="n">
         <v>46300</v>
       </c>
@@ -13129,6 +12972,7 @@
         <v>2</v>
       </c>
       <c r="P203" s="10" t="n">
+        <f aca="false">IF(OR(M203="",M203=0),"",IF(N203="",0,N203)/M203)</f>
         <v>0</v>
       </c>
       <c r="Q203" s="7"/>
@@ -13149,32 +12993,60 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="8" t="n">
         <v>46307</v>
       </c>
-      <c r="B204" s="6"/>
-      <c r="C204" s="6"/>
-      <c r="D204" s="6"/>
-      <c r="E204" s="6"/>
-      <c r="F204" s="6"/>
-      <c r="G204" s="6"/>
-      <c r="H204" s="6"/>
-      <c r="I204" s="6"/>
-      <c r="J204" s="6"/>
-      <c r="K204" s="6"/>
-      <c r="L204" s="6"/>
-      <c r="M204" s="5" t="str">
+      <c r="B204" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C204" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D204" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H204" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I204" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L204" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M204" s="5" t="n">
         <f aca="false">IF(AND(K204="",L204=""),"",SUM(K204:L204))</f>
-        <v/>
-      </c>
-      <c r="N204" s="6"/>
-      <c r="O204" s="6"/>
-      <c r="P204" s="10" t="str">
+        <v>8</v>
+      </c>
+      <c r="N204" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P204" s="10" t="n">
         <f aca="false">IF(OR(M204="",M204=0),"",IF(N204="",0,N204)/M204)</f>
-        <v/>
-      </c>
-      <c r="Q204" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q204" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="R204" s="11" t="n">
         <f aca="false">A204+5</f>
         <v>46312</v>
@@ -13192,30 +13064,56 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="B205" s="6"/>
-      <c r="C205" s="6"/>
-      <c r="D205" s="6"/>
-      <c r="E205" s="6"/>
-      <c r="F205" s="6"/>
-      <c r="G205" s="6"/>
-      <c r="H205" s="6"/>
-      <c r="I205" s="6"/>
-      <c r="J205" s="6"/>
-      <c r="K205" s="6"/>
-      <c r="L205" s="6"/>
-      <c r="M205" s="5" t="str">
+      <c r="B205" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D205" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H205" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I205" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J205" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L205" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M205" s="5" t="n">
         <f aca="false">IF(AND(K205="",L205=""),"",SUM(K205:L205))</f>
-        <v/>
-      </c>
-      <c r="N205" s="6"/>
-      <c r="O205" s="6"/>
-      <c r="P205" s="10" t="str">
+        <v>4</v>
+      </c>
+      <c r="N205" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O205" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P205" s="10" t="n">
         <f aca="false">IF(OR(M205="",M205=0),"",IF(N205="",0,N205)/M205)</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="Q205" s="7"/>
       <c r="R205" s="11" t="n">
@@ -13235,7 +13133,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="8" t="n">
         <v>46321</v>
       </c>
@@ -13278,7 +13176,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="8" t="n">
         <v>46328</v>
       </c>
@@ -13321,7 +13219,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="8" t="n">
         <v>46335</v>
       </c>
@@ -13364,7 +13262,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="8" t="n">
         <v>46342</v>
       </c>
@@ -13407,7 +13305,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="8" t="n">
         <v>46349</v>
       </c>
@@ -13450,7 +13348,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="8" t="n">
         <v>46356</v>
       </c>
@@ -13493,7 +13391,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="8" t="n">
         <v>46363</v>
       </c>
@@ -13536,7 +13434,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="8" t="n">
         <v>46370</v>
       </c>
@@ -13579,7 +13477,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="8" t="n">
         <v>46377</v>
       </c>
@@ -13622,7 +13520,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="8" t="n">
         <v>46384</v>
       </c>
@@ -13665,7 +13563,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="8" t="n">
         <v>46391</v>
       </c>
@@ -13708,7 +13606,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="8" t="n">
         <v>46398</v>
       </c>
@@ -13751,7 +13649,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="8" t="n">
         <v>46405</v>
       </c>
@@ -13794,7 +13692,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="8" t="n">
         <v>46412</v>
       </c>
@@ -13837,7 +13735,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="8" t="n">
         <v>46419</v>
       </c>
@@ -13880,7 +13778,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="8" t="n">
         <v>46426</v>
       </c>
@@ -13923,7 +13821,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="8" t="n">
         <v>46433</v>
       </c>
@@ -13966,7 +13864,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="8" t="n">
         <v>46440</v>
       </c>
@@ -14009,7 +13907,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="8" t="n">
         <v>46447</v>
       </c>
@@ -14052,7 +13950,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="8" t="n">
         <v>46454</v>
       </c>
@@ -14095,7 +13993,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="8" t="n">
         <v>46461</v>
       </c>
@@ -14138,7 +14036,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="8" t="n">
         <v>46468</v>
       </c>
@@ -14181,7 +14079,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="8" t="n">
         <v>46475</v>
       </c>
@@ -14224,7 +14122,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="8" t="n">
         <v>46482</v>
       </c>
@@ -14267,7 +14165,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="8" t="n">
         <v>46489</v>
       </c>
@@ -14310,7 +14208,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="8" t="n">
         <v>46496</v>
       </c>
@@ -14353,7 +14251,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="8" t="n">
         <v>46503</v>
       </c>
@@ -14396,7 +14294,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="8" t="n">
         <v>46510</v>
       </c>
@@ -14439,7 +14337,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="8" t="n">
         <v>46517</v>
       </c>
@@ -14482,7 +14380,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="8" t="n">
         <v>46524</v>
       </c>
@@ -14525,7 +14423,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="8" t="n">
         <v>46531</v>
       </c>
@@ -14568,7 +14466,7 @@
         <v>2026-27</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="8" t="n">
         <v>46538</v>
       </c>
@@ -14638,7 +14536,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>62</v>
@@ -14668,10 +14566,10 @@
         <v>70</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="n">
         <v>45285</v>
       </c>
@@ -14707,7 +14605,7 @@
       </c>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
         <v>45292</v>
       </c>
@@ -14743,7 +14641,7 @@
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
         <v>45299</v>
       </c>
@@ -14779,7 +14677,7 @@
       </c>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>45306</v>
       </c>
@@ -14815,7 +14713,7 @@
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
         <v>45313</v>
       </c>
@@ -14851,7 +14749,7 @@
       </c>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>45320</v>
       </c>
@@ -14887,7 +14785,7 @@
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>45327</v>
       </c>
@@ -14923,7 +14821,7 @@
       </c>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>45334</v>
       </c>
@@ -14959,7 +14857,7 @@
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
         <v>45341</v>
       </c>
@@ -14995,7 +14893,7 @@
       </c>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>45348</v>
       </c>
@@ -15031,7 +14929,7 @@
       </c>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>45355</v>
       </c>
@@ -15067,7 +14965,7 @@
       </c>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>45537</v>
       </c>
@@ -15103,7 +15001,7 @@
       </c>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>45544</v>
       </c>
@@ -15139,7 +15037,7 @@
       </c>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>45551</v>
       </c>
@@ -15175,7 +15073,7 @@
       </c>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>45558</v>
       </c>
@@ -15211,7 +15109,7 @@
       </c>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>45565</v>
       </c>
@@ -15247,7 +15145,7 @@
       </c>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
         <v>45572</v>
       </c>
@@ -15283,7 +15181,7 @@
       </c>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>45579</v>
       </c>
@@ -15319,7 +15217,7 @@
       </c>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
         <v>45586</v>
       </c>
@@ -15355,7 +15253,7 @@
       </c>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
         <v>45593</v>
       </c>
@@ -15391,7 +15289,7 @@
       </c>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
         <v>45600</v>
       </c>
@@ -15427,7 +15325,7 @@
       </c>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
         <v>45607</v>
       </c>
@@ -15463,7 +15361,7 @@
       </c>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
         <v>45614</v>
       </c>
@@ -15499,7 +15397,7 @@
       </c>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
         <v>45621</v>
       </c>
@@ -15535,7 +15433,7 @@
       </c>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
         <v>45628</v>
       </c>
@@ -15571,7 +15469,7 @@
       </c>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>45635</v>
       </c>
@@ -15607,7 +15505,7 @@
       </c>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
         <v>45642</v>
       </c>
@@ -15643,7 +15541,7 @@
       </c>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
         <v>45649</v>
       </c>
@@ -15679,7 +15577,7 @@
       </c>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
         <v>45656</v>
       </c>
@@ -15715,7 +15613,7 @@
       </c>
       <c r="K30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
         <v>45663</v>
       </c>
@@ -15751,7 +15649,7 @@
       </c>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
         <v>45670</v>
       </c>
@@ -15787,7 +15685,7 @@
       </c>
       <c r="K32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
         <v>45677</v>
       </c>
@@ -15823,7 +15721,7 @@
       </c>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
         <v>45684</v>
       </c>
@@ -15859,7 +15757,7 @@
       </c>
       <c r="K34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
         <v>45691</v>
       </c>
@@ -15895,7 +15793,7 @@
       </c>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
         <v>45698</v>
       </c>
@@ -15931,7 +15829,7 @@
       </c>
       <c r="K36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
         <v>45705</v>
       </c>
@@ -15967,7 +15865,7 @@
       </c>
       <c r="K37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
         <v>45712</v>
       </c>
@@ -16003,7 +15901,7 @@
       </c>
       <c r="K38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
         <v>45719</v>
       </c>
@@ -16039,7 +15937,7 @@
       </c>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
         <v>45726</v>
       </c>
@@ -16075,7 +15973,7 @@
       </c>
       <c r="K40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
         <v>45733</v>
       </c>
@@ -16111,7 +16009,7 @@
       </c>
       <c r="K41" s="7"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
         <v>45740</v>
       </c>
@@ -16147,7 +16045,7 @@
       </c>
       <c r="K42" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
         <v>45901</v>
       </c>
@@ -16183,7 +16081,7 @@
       </c>
       <c r="K43" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
         <v>45908</v>
       </c>
@@ -16219,7 +16117,7 @@
       </c>
       <c r="K44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
         <v>45915</v>
       </c>
@@ -16255,7 +16153,7 @@
       </c>
       <c r="K45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
         <v>45922</v>
       </c>
@@ -16291,7 +16189,7 @@
       </c>
       <c r="K46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
         <v>45929</v>
       </c>
@@ -16327,7 +16225,7 @@
       </c>
       <c r="K47" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
         <v>45936</v>
       </c>
@@ -16363,7 +16261,7 @@
       </c>
       <c r="K48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
         <v>45943</v>
       </c>
@@ -16399,7 +16297,7 @@
       </c>
       <c r="K49" s="7"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
         <v>45950</v>
       </c>
@@ -16435,7 +16333,7 @@
       </c>
       <c r="K50" s="7"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
         <v>45957</v>
       </c>
@@ -16471,7 +16369,7 @@
       </c>
       <c r="K51" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
         <v>45964</v>
       </c>
@@ -16507,7 +16405,7 @@
       </c>
       <c r="K52" s="7"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
         <v>45971</v>
       </c>
@@ -16543,7 +16441,7 @@
       </c>
       <c r="K53" s="7"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
         <v>45978</v>
       </c>
@@ -16579,7 +16477,7 @@
       </c>
       <c r="K54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
         <v>45985</v>
       </c>
@@ -16615,7 +16513,7 @@
       </c>
       <c r="K55" s="7"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
         <v>45992</v>
       </c>
@@ -16651,7 +16549,7 @@
       </c>
       <c r="K56" s="7"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
         <v>45999</v>
       </c>
@@ -16687,7 +16585,7 @@
       </c>
       <c r="K57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
         <v>46006</v>
       </c>
@@ -16723,7 +16621,7 @@
       </c>
       <c r="K58" s="7"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
         <v>46013</v>
       </c>
@@ -16759,7 +16657,7 @@
       </c>
       <c r="K59" s="7"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
         <v>46020</v>
       </c>
@@ -16795,7 +16693,7 @@
       </c>
       <c r="K60" s="7"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
         <v>46027</v>
       </c>
@@ -16831,7 +16729,7 @@
       </c>
       <c r="K61" s="7"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
         <v>46034</v>
       </c>
@@ -16867,7 +16765,7 @@
       </c>
       <c r="K62" s="7"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
         <v>46041</v>
       </c>
@@ -16903,7 +16801,7 @@
       </c>
       <c r="K63" s="7"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
         <v>46048</v>
       </c>
@@ -16939,7 +16837,7 @@
       </c>
       <c r="K64" s="7"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
         <v>46055</v>
       </c>
@@ -16975,7 +16873,7 @@
       </c>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
         <v>46062</v>
       </c>
@@ -17011,7 +16909,7 @@
       </c>
       <c r="K66" s="7"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
         <v>46069</v>
       </c>
@@ -17047,7 +16945,7 @@
       </c>
       <c r="K67" s="7"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
         <v>46076</v>
       </c>
@@ -17083,7 +16981,7 @@
       </c>
       <c r="K68" s="7"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
         <v>46083</v>
       </c>
@@ -17119,7 +17017,7 @@
       </c>
       <c r="K69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
         <v>46090</v>
       </c>
@@ -17155,7 +17053,7 @@
       </c>
       <c r="K70" s="7"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
         <v>46097</v>
       </c>
@@ -17191,7 +17089,7 @@
       </c>
       <c r="K71" s="7"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
         <v>46104</v>
       </c>
@@ -17227,7 +17125,7 @@
       </c>
       <c r="K72" s="7"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
         <v>46272</v>
       </c>
@@ -17265,7 +17163,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
         <v>46279</v>
       </c>
@@ -17301,7 +17199,7 @@
       </c>
       <c r="K74" s="7"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
         <v>46286</v>
       </c>
@@ -17337,7 +17235,7 @@
       </c>
       <c r="K75" s="7"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
         <v>46293</v>
       </c>
@@ -17373,7 +17271,7 @@
       </c>
       <c r="K76" s="7"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
         <v>46300</v>
       </c>
@@ -17409,55 +17307,79 @@
       </c>
       <c r="K77" s="7"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
         <v>46307</v>
       </c>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="10" t="str">
+      <c r="B78" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D78" s="10" t="n">
         <f aca="false">IF(SUM(B78:C78)=0,"",B78/SUM(B78:C78))</f>
-        <v/>
-      </c>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="10" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G78" s="10" t="n">
         <f aca="false">IF(SUM(E78:F78)=0,"",E78/SUM(E78:F78))</f>
-        <v/>
-      </c>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="10" t="str">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J78" s="10" t="n">
         <f aca="false">IF(SUM(H78:I78)=0,"",H78/SUM(H78:I78))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K78" s="7"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="10" t="str">
+      <c r="B79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D79" s="10" t="n">
         <f aca="false">IF(SUM(B79:C79)=0,"",B79/SUM(B79:C79))</f>
-        <v/>
-      </c>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="10" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G79" s="10" t="n">
         <f aca="false">IF(SUM(E79:F79)=0,"",E79/SUM(E79:F79))</f>
-        <v/>
-      </c>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="10" t="str">
+        <v>0.230769230769231</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J79" s="10" t="n">
         <f aca="false">IF(SUM(H79:I79)=0,"",H79/SUM(H79:I79))</f>
-        <v/>
+        <v>0.0833333333333333</v>
       </c>
       <c r="K79" s="7"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
         <v>46321</v>
       </c>
@@ -17481,7 +17403,7 @@
       </c>
       <c r="K80" s="7"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
         <v>46328</v>
       </c>
@@ -17505,7 +17427,7 @@
       </c>
       <c r="K81" s="7"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
         <v>46335</v>
       </c>
@@ -17529,7 +17451,7 @@
       </c>
       <c r="K82" s="7"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
         <v>46342</v>
       </c>
@@ -17553,7 +17475,7 @@
       </c>
       <c r="K83" s="7"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="n">
         <v>46349</v>
       </c>
@@ -17577,7 +17499,7 @@
       </c>
       <c r="K84" s="7"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="n">
         <v>46356</v>
       </c>
@@ -17601,7 +17523,7 @@
       </c>
       <c r="K85" s="7"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="n">
         <v>46363</v>
       </c>
@@ -17625,7 +17547,7 @@
       </c>
       <c r="K86" s="7"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="n">
         <v>46370</v>
       </c>
@@ -17649,7 +17571,7 @@
       </c>
       <c r="K87" s="7"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="n">
         <v>46377</v>
       </c>
@@ -17673,7 +17595,7 @@
       </c>
       <c r="K88" s="7"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="n">
         <v>46384</v>
       </c>
@@ -17697,7 +17619,7 @@
       </c>
       <c r="K89" s="7"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="n">
         <v>46391</v>
       </c>
@@ -17721,7 +17643,7 @@
       </c>
       <c r="K90" s="7"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="n">
         <v>46398</v>
       </c>
@@ -17745,7 +17667,7 @@
       </c>
       <c r="K91" s="7"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="n">
         <v>46405</v>
       </c>
@@ -17769,7 +17691,7 @@
       </c>
       <c r="K92" s="7"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="n">
         <v>46412</v>
       </c>
@@ -17793,7 +17715,7 @@
       </c>
       <c r="K93" s="7"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="n">
         <v>46419</v>
       </c>
@@ -17817,7 +17739,7 @@
       </c>
       <c r="K94" s="7"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="n">
         <v>46426</v>
       </c>
@@ -17841,7 +17763,7 @@
       </c>
       <c r="K95" s="7"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="n">
         <v>46433</v>
       </c>
@@ -17865,7 +17787,7 @@
       </c>
       <c r="K96" s="7"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="n">
         <v>46440</v>
       </c>
@@ -17889,7 +17811,7 @@
       </c>
       <c r="K97" s="7"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="n">
         <v>46447</v>
       </c>
@@ -17913,7 +17835,7 @@
       </c>
       <c r="K98" s="7"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="n">
         <v>46454</v>
       </c>
@@ -17937,7 +17859,7 @@
       </c>
       <c r="K99" s="7"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="n">
         <v>46461</v>
       </c>
@@ -17961,7 +17883,7 @@
       </c>
       <c r="K100" s="7"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="n">
         <v>46468</v>
       </c>
@@ -17985,7 +17907,7 @@
       </c>
       <c r="K101" s="7"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="n">
         <v>46475</v>
       </c>
@@ -18009,7 +17931,7 @@
       </c>
       <c r="K102" s="7"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="n">
         <v>46482</v>
       </c>
@@ -18033,7 +17955,7 @@
       </c>
       <c r="K103" s="7"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="n">
         <v>46489</v>
       </c>
@@ -18057,7 +17979,7 @@
       </c>
       <c r="K104" s="7"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="n">
         <v>46496</v>
       </c>
@@ -18081,7 +18003,7 @@
       </c>
       <c r="K105" s="7"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="8" t="n">
         <v>46503</v>
       </c>
@@ -18105,7 +18027,7 @@
       </c>
       <c r="K106" s="7"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="n">
         <v>46510</v>
       </c>
@@ -18129,7 +18051,7 @@
       </c>
       <c r="K107" s="7"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="n">
         <v>46517</v>
       </c>
@@ -18153,7 +18075,7 @@
       </c>
       <c r="K108" s="7"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="n">
         <v>46524</v>
       </c>
@@ -18177,7 +18099,7 @@
       </c>
       <c r="K109" s="7"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="n">
         <v>46531</v>
       </c>
@@ -18201,7 +18123,7 @@
       </c>
       <c r="K110" s="7"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="n">
         <v>46538</v>
       </c>
@@ -18249,19 +18171,19 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>74</v>
@@ -18276,13 +18198,13 @@
         <v>77</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
         <v>36</v>
       </c>
@@ -18310,7 +18232,7 @@
         <v>9/7/26 – 9/13/26</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>37</v>
       </c>
@@ -18339,7 +18261,7 @@
         <v>9/14/26 – 9/20/26</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>38</v>
       </c>
@@ -18368,7 +18290,7 @@
         <v>9/21/26 – 9/27/26</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
         <v>39</v>
       </c>
@@ -18397,7 +18319,7 @@
         <v>9/28/26 – 10/4/26</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
         <v>40</v>
       </c>
@@ -18426,7 +18348,7 @@
         <v>10/5/26 – 10/11/26</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>41</v>
       </c>
@@ -18446,16 +18368,16 @@
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A10,Weekly_Local!$B:$B,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$B:$B,Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A10))</f>
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="str">
+      <c r="F10" s="5" t="n">
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A10,Weekly_Local!$B:$B,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$B:$B,Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A10))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="G10" s="5" t="str">
         <f aca="false">IF(AND($A10=53,DATE(YEAR(Config!$B$3),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3),1,4))+1+364&gt;=DATE(YEAR(Config!$B$3)+1,1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+1,1,4))+1),"",TEXT(DATE(YEAR(Config!$B$3)+IF($A10&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A10&gt;=36,0,1),1,4))+1+7*($A10-1)+1,"m/d/yy")&amp;" – "&amp;TEXT(DATE(YEAR(Config!$B$3)+IF($A10&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A10&gt;=36,0,1),1,4))+1+7*($A10-1)+7,"m/d/yy"))</f>
         <v>10/12/26 – 10/18/26</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="n">
         <v>42</v>
       </c>
@@ -18475,16 +18397,16 @@
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A11,Weekly_Local!$B:$B,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$B:$B,Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A11))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="5" t="str">
+      <c r="F11" s="5" t="n">
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A11,Weekly_Local!$B:$B,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$B:$B,Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A11))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G11" s="5" t="str">
         <f aca="false">IF(AND($A11=53,DATE(YEAR(Config!$B$3),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3),1,4))+1+364&gt;=DATE(YEAR(Config!$B$3)+1,1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+1,1,4))+1),"",TEXT(DATE(YEAR(Config!$B$3)+IF($A11&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A11&gt;=36,0,1),1,4))+1+7*($A11-1)+1,"m/d/yy")&amp;" – "&amp;TEXT(DATE(YEAR(Config!$B$3)+IF($A11&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A11&gt;=36,0,1),1,4))+1+7*($A11-1)+7,"m/d/yy"))</f>
         <v>10/19/26 – 10/25/26</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
         <v>43</v>
       </c>
@@ -18513,7 +18435,7 @@
         <v>10/26/26 – 11/1/26</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
         <v>44</v>
       </c>
@@ -18542,7 +18464,7 @@
         <v>11/2/26 – 11/8/26</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>45</v>
       </c>
@@ -18571,7 +18493,7 @@
         <v>11/9/26 – 11/15/26</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
         <v>46</v>
       </c>
@@ -18600,7 +18522,7 @@
         <v>11/16/26 – 11/22/26</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>47</v>
       </c>
@@ -18629,7 +18551,7 @@
         <v>11/23/26 – 11/29/26</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>48</v>
       </c>
@@ -18658,7 +18580,7 @@
         <v>11/30/26 – 12/6/26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>49</v>
       </c>
@@ -18687,7 +18609,7 @@
         <v>12/7/26 – 12/13/26</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>50</v>
       </c>
@@ -18716,7 +18638,7 @@
         <v>12/14/26 – 12/20/26</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>51</v>
       </c>
@@ -18745,7 +18667,7 @@
         <v>12/21/26 – 12/27/26</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>52</v>
       </c>
@@ -18774,7 +18696,7 @@
         <v>12/28/26 – 1/3/27</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>53</v>
       </c>
@@ -18803,7 +18725,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
         <v>1</v>
       </c>
@@ -18832,7 +18754,7 @@
         <v>1/4/27 – 1/10/27</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>2</v>
       </c>
@@ -18861,7 +18783,7 @@
         <v>1/11/27 – 1/17/27</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>3</v>
       </c>
@@ -18890,7 +18812,7 @@
         <v>1/18/27 – 1/24/27</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>4</v>
       </c>
@@ -18919,7 +18841,7 @@
         <v>1/25/27 – 1/31/27</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>5</v>
       </c>
@@ -18948,7 +18870,7 @@
         <v>2/1/27 – 2/7/27</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>6</v>
       </c>
@@ -18977,7 +18899,7 @@
         <v>2/8/27 – 2/14/27</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
         <v>7</v>
       </c>
@@ -19006,7 +18928,7 @@
         <v>2/15/27 – 2/21/27</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>8</v>
       </c>
@@ -19035,7 +18957,7 @@
         <v>2/22/27 – 2/28/27</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
         <v>9</v>
       </c>
@@ -19064,7 +18986,7 @@
         <v>3/1/27 – 3/7/27</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>10</v>
       </c>
@@ -19093,7 +19015,7 @@
         <v>3/8/27 – 3/14/27</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
         <v>11</v>
       </c>
@@ -19122,7 +19044,7 @@
         <v>3/15/27 – 3/21/27</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
         <v>12</v>
       </c>
@@ -19151,7 +19073,7 @@
         <v>3/22/27 – 3/28/27</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
         <v>13</v>
       </c>
@@ -19180,7 +19102,7 @@
         <v>3/29/27 – 4/4/27</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
         <v>14</v>
       </c>
@@ -19209,7 +19131,7 @@
         <v>4/5/27 – 4/11/27</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="n">
         <v>15</v>
       </c>
@@ -19238,7 +19160,7 @@
         <v>4/12/27 – 4/18/27</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
         <v>16</v>
       </c>
@@ -19267,7 +19189,7 @@
         <v>4/19/27 – 4/25/27</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="n">
         <v>17</v>
       </c>
@@ -19296,7 +19218,7 @@
         <v>4/26/27 – 5/2/27</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="n">
         <v>18</v>
       </c>
@@ -19325,7 +19247,7 @@
         <v>5/3/27 – 5/9/27</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="n">
         <v>19</v>
       </c>
@@ -19354,7 +19276,7 @@
         <v>5/10/27 – 5/16/27</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
         <v>20</v>
       </c>
@@ -19383,7 +19305,7 @@
         <v>5/17/27 – 5/23/27</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="n">
         <v>21</v>
       </c>
@@ -19412,7 +19334,7 @@
         <v>5/24/27 – 5/30/27</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="n">
         <v>22</v>
       </c>
@@ -19441,7 +19363,7 @@
         <v>5/31/27 – 6/6/27</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="n">
         <v>23</v>
       </c>
@@ -19470,7 +19392,7 @@
         <v>6/7/27 – 6/13/27</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="n">
         <v>24</v>
       </c>
@@ -19499,7 +19421,7 @@
         <v>6/14/27 – 6/20/27</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="n">
         <v>25</v>
       </c>
@@ -19528,7 +19450,7 @@
         <v>6/21/27 – 6/27/27</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
         <v>26</v>
       </c>
@@ -19557,7 +19479,7 @@
         <v>6/28/27 – 7/4/27</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
         <v>27</v>
       </c>
@@ -19586,7 +19508,7 @@
         <v>7/5/27 – 7/11/27</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="n">
         <v>28</v>
       </c>
@@ -19615,7 +19537,7 @@
         <v>7/12/27 – 7/18/27</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="n">
         <v>29</v>
       </c>
@@ -19644,7 +19566,7 @@
         <v>7/19/27 – 7/25/27</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="n">
         <v>30</v>
       </c>
@@ -19673,7 +19595,7 @@
         <v>7/26/27 – 8/1/27</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="n">
         <v>31</v>
       </c>
@@ -19702,7 +19624,7 @@
         <v>8/2/27 – 8/8/27</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="n">
         <v>32</v>
       </c>
@@ -19731,7 +19653,7 @@
         <v>8/9/27 – 8/15/27</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="n">
         <v>33</v>
       </c>
@@ -19760,7 +19682,7 @@
         <v>8/16/27 – 8/22/27</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="n">
         <v>34</v>
       </c>
@@ -19789,7 +19711,7 @@
         <v>8/23/27 – 8/29/27</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="n">
         <v>35</v>
       </c>
@@ -19818,14 +19740,14 @@
         <v>8/30/27 – 9/5/27</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>74</v>
@@ -19840,13 +19762,13 @@
         <v>77</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="n">
         <v>36</v>
       </c>
@@ -19874,7 +19796,7 @@
         <v>9/7/26 – 9/13/26</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="n">
         <v>37</v>
       </c>
@@ -19903,7 +19825,7 @@
         <v>9/14/26 – 9/20/26</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="n">
         <v>38</v>
       </c>
@@ -19932,7 +19854,7 @@
         <v>9/21/26 – 9/27/26</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="n">
         <v>39</v>
       </c>
@@ -19961,7 +19883,7 @@
         <v>9/28/26 – 10/4/26</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="n">
         <v>40</v>
       </c>
@@ -19990,7 +19912,7 @@
         <v>10/5/26 – 10/11/26</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="n">
         <v>41</v>
       </c>
@@ -20010,16 +19932,16 @@
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A67,Weekly_Local!$C:$C,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$C:$C,Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A67))</f>
         <v>0</v>
       </c>
-      <c r="F67" s="5" t="str">
+      <c r="F67" s="5" t="n">
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A67,Weekly_Local!$C:$C,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$C:$C,Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A67))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G67" s="5" t="str">
         <f aca="false">IF(AND($A67=53,DATE(YEAR(Config!$B$3),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3),1,4))+1+364&gt;=DATE(YEAR(Config!$B$3)+1,1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+1,1,4))+1),"",TEXT(DATE(YEAR(Config!$B$3)+IF($A67&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A67&gt;=36,0,1),1,4))+1+7*($A67-1)+1,"m/d/yy")&amp;" – "&amp;TEXT(DATE(YEAR(Config!$B$3)+IF($A67&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A67&gt;=36,0,1),1,4))+1+7*($A67-1)+7,"m/d/yy"))</f>
         <v>10/12/26 – 10/18/26</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="n">
         <v>42</v>
       </c>
@@ -20039,16 +19961,16 @@
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A68,Weekly_Local!$C:$C,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$C:$C,Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A68))</f>
         <v>0</v>
       </c>
-      <c r="F68" s="5" t="str">
+      <c r="F68" s="5" t="n">
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A68,Weekly_Local!$C:$C,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$C:$C,Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A68))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G68" s="5" t="str">
         <f aca="false">IF(AND($A68=53,DATE(YEAR(Config!$B$3),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3),1,4))+1+364&gt;=DATE(YEAR(Config!$B$3)+1,1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+1,1,4))+1),"",TEXT(DATE(YEAR(Config!$B$3)+IF($A68&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A68&gt;=36,0,1),1,4))+1+7*($A68-1)+1,"m/d/yy")&amp;" – "&amp;TEXT(DATE(YEAR(Config!$B$3)+IF($A68&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A68&gt;=36,0,1),1,4))+1+7*($A68-1)+7,"m/d/yy"))</f>
         <v>10/19/26 – 10/25/26</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="n">
         <v>43</v>
       </c>
@@ -20077,7 +19999,7 @@
         <v>10/26/26 – 11/1/26</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="n">
         <v>44</v>
       </c>
@@ -20106,7 +20028,7 @@
         <v>11/2/26 – 11/8/26</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="n">
         <v>45</v>
       </c>
@@ -20135,7 +20057,7 @@
         <v>11/9/26 – 11/15/26</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="n">
         <v>46</v>
       </c>
@@ -20164,7 +20086,7 @@
         <v>11/16/26 – 11/22/26</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="n">
         <v>47</v>
       </c>
@@ -20193,7 +20115,7 @@
         <v>11/23/26 – 11/29/26</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="n">
         <v>48</v>
       </c>
@@ -20222,7 +20144,7 @@
         <v>11/30/26 – 12/6/26</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
         <v>49</v>
       </c>
@@ -20251,7 +20173,7 @@
         <v>12/7/26 – 12/13/26</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="n">
         <v>50</v>
       </c>
@@ -20280,7 +20202,7 @@
         <v>12/14/26 – 12/20/26</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="n">
         <v>51</v>
       </c>
@@ -20309,7 +20231,7 @@
         <v>12/21/26 – 12/27/26</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
         <v>52</v>
       </c>
@@ -20338,7 +20260,7 @@
         <v>12/28/26 – 1/3/27</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="n">
         <v>53</v>
       </c>
@@ -20367,7 +20289,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="n">
         <v>1</v>
       </c>
@@ -20396,7 +20318,7 @@
         <v>1/4/27 – 1/10/27</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="n">
         <v>2</v>
       </c>
@@ -20425,7 +20347,7 @@
         <v>1/11/27 – 1/17/27</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="n">
         <v>3</v>
       </c>
@@ -20454,7 +20376,7 @@
         <v>1/18/27 – 1/24/27</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="n">
         <v>4</v>
       </c>
@@ -20483,7 +20405,7 @@
         <v>1/25/27 – 1/31/27</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="n">
         <v>5</v>
       </c>
@@ -20512,7 +20434,7 @@
         <v>2/1/27 – 2/7/27</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="n">
         <v>6</v>
       </c>
@@ -20541,7 +20463,7 @@
         <v>2/8/27 – 2/14/27</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
         <v>7</v>
       </c>
@@ -20570,7 +20492,7 @@
         <v>2/15/27 – 2/21/27</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="n">
         <v>8</v>
       </c>
@@ -20599,7 +20521,7 @@
         <v>2/22/27 – 2/28/27</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
         <v>9</v>
       </c>
@@ -20628,7 +20550,7 @@
         <v>3/1/27 – 3/7/27</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="n">
         <v>10</v>
       </c>
@@ -20657,7 +20579,7 @@
         <v>3/8/27 – 3/14/27</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="n">
         <v>11</v>
       </c>
@@ -20686,7 +20608,7 @@
         <v>3/15/27 – 3/21/27</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="n">
         <v>12</v>
       </c>
@@ -20715,7 +20637,7 @@
         <v>3/22/27 – 3/28/27</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="n">
         <v>13</v>
       </c>
@@ -20744,7 +20666,7 @@
         <v>3/29/27 – 4/4/27</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="n">
         <v>14</v>
       </c>
@@ -20773,7 +20695,7 @@
         <v>4/5/27 – 4/11/27</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="n">
         <v>15</v>
       </c>
@@ -20802,7 +20724,7 @@
         <v>4/12/27 – 4/18/27</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="n">
         <v>16</v>
       </c>
@@ -20831,7 +20753,7 @@
         <v>4/19/27 – 4/25/27</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="n">
         <v>17</v>
       </c>
@@ -20860,7 +20782,7 @@
         <v>4/26/27 – 5/2/27</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="n">
         <v>18</v>
       </c>
@@ -20889,7 +20811,7 @@
         <v>5/3/27 – 5/9/27</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="n">
         <v>19</v>
       </c>
@@ -20918,7 +20840,7 @@
         <v>5/10/27 – 5/16/27</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="n">
         <v>20</v>
       </c>
@@ -20947,7 +20869,7 @@
         <v>5/17/27 – 5/23/27</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="n">
         <v>21</v>
       </c>
@@ -20976,7 +20898,7 @@
         <v>5/24/27 – 5/30/27</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="n">
         <v>22</v>
       </c>
@@ -21005,7 +20927,7 @@
         <v>5/31/27 – 6/6/27</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="n">
         <v>23</v>
       </c>
@@ -21034,7 +20956,7 @@
         <v>6/7/27 – 6/13/27</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="n">
         <v>24</v>
       </c>
@@ -21063,7 +20985,7 @@
         <v>6/14/27 – 6/20/27</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="n">
         <v>25</v>
       </c>
@@ -21092,7 +21014,7 @@
         <v>6/21/27 – 6/27/27</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="n">
         <v>26</v>
       </c>
@@ -21121,7 +21043,7 @@
         <v>6/28/27 – 7/4/27</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="n">
         <v>27</v>
       </c>
@@ -21150,7 +21072,7 @@
         <v>7/5/27 – 7/11/27</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="n">
         <v>28</v>
       </c>
@@ -21179,7 +21101,7 @@
         <v>7/12/27 – 7/18/27</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="n">
         <v>29</v>
       </c>
@@ -21208,7 +21130,7 @@
         <v>7/19/27 – 7/25/27</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="n">
         <v>30</v>
       </c>
@@ -21237,7 +21159,7 @@
         <v>7/26/27 – 8/1/27</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="n">
         <v>31</v>
       </c>
@@ -21266,7 +21188,7 @@
         <v>8/2/27 – 8/8/27</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="n">
         <v>32</v>
       </c>
@@ -21295,7 +21217,7 @@
         <v>8/9/27 – 8/15/27</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="n">
         <v>33</v>
       </c>
@@ -21324,7 +21246,7 @@
         <v>8/16/27 – 8/22/27</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="n">
         <v>34</v>
       </c>
@@ -21353,7 +21275,7 @@
         <v>8/23/27 – 8/29/27</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="n">
         <v>35</v>
       </c>
@@ -21382,14 +21304,14 @@
         <v>8/30/27 – 9/5/27</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>74</v>
@@ -21404,13 +21326,13 @@
         <v>77</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="n">
         <v>36</v>
       </c>
@@ -21438,7 +21360,7 @@
         <v>9/7/26 – 9/13/26</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="n">
         <v>37</v>
       </c>
@@ -21467,7 +21389,7 @@
         <v>9/14/26 – 9/20/26</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="n">
         <v>38</v>
       </c>
@@ -21496,7 +21418,7 @@
         <v>9/21/26 – 9/27/26</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="n">
         <v>39</v>
       </c>
@@ -21525,7 +21447,7 @@
         <v>9/28/26 – 10/4/26</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="n">
         <v>40</v>
       </c>
@@ -21554,7 +21476,7 @@
         <v>10/5/26 – 10/11/26</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="n">
         <v>41</v>
       </c>
@@ -21574,16 +21496,16 @@
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A124,Weekly_Local!$D:$D,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$D:$D,Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A124))</f>
         <v>0</v>
       </c>
-      <c r="F124" s="5" t="str">
+      <c r="F124" s="5" t="n">
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A124,Weekly_Local!$D:$D,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$D:$D,Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A124))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G124" s="5" t="str">
         <f aca="false">IF(AND($A124=53,DATE(YEAR(Config!$B$3),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3),1,4))+1+364&gt;=DATE(YEAR(Config!$B$3)+1,1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+1,1,4))+1),"",TEXT(DATE(YEAR(Config!$B$3)+IF($A124&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A124&gt;=36,0,1),1,4))+1+7*($A124-1)+1,"m/d/yy")&amp;" – "&amp;TEXT(DATE(YEAR(Config!$B$3)+IF($A124&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A124&gt;=36,0,1),1,4))+1+7*($A124-1)+7,"m/d/yy"))</f>
         <v>10/12/26 – 10/18/26</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="n">
         <v>42</v>
       </c>
@@ -21603,16 +21525,16 @@
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A125,Weekly_Local!$D:$D,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$D:$D,Weekly_Local!$U:$U,"2025-26",Weekly_Local!$T:$T,$A125))</f>
         <v>0</v>
       </c>
-      <c r="F125" s="5" t="str">
+      <c r="F125" s="5" t="n">
         <f aca="false">IF(COUNTIFS(Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A125,Weekly_Local!$D:$D,"&lt;&gt;")=0,"",SUMIFS(Weekly_Local!$D:$D,Weekly_Local!$U:$U,"2026-27",Weekly_Local!$T:$T,$A125))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G125" s="5" t="str">
         <f aca="false">IF(AND($A125=53,DATE(YEAR(Config!$B$3),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3),1,4))+1+364&gt;=DATE(YEAR(Config!$B$3)+1,1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+1,1,4))+1),"",TEXT(DATE(YEAR(Config!$B$3)+IF($A125&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A125&gt;=36,0,1),1,4))+1+7*($A125-1)+1,"m/d/yy")&amp;" – "&amp;TEXT(DATE(YEAR(Config!$B$3)+IF($A125&gt;=36,0,1),1,4)-WEEKDAY(DATE(YEAR(Config!$B$3)+IF($A125&gt;=36,0,1),1,4))+1+7*($A125-1)+7,"m/d/yy"))</f>
         <v>10/19/26 – 10/25/26</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="n">
         <v>43</v>
       </c>
@@ -21641,7 +21563,7 @@
         <v>10/26/26 – 11/1/26</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="n">
         <v>44</v>
       </c>
@@ -21670,7 +21592,7 @@
         <v>11/2/26 – 11/8/26</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="5" t="n">
         <v>45</v>
       </c>
@@ -21699,7 +21621,7 @@
         <v>11/9/26 – 11/15/26</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="n">
         <v>46</v>
       </c>
@@ -21728,7 +21650,7 @@
         <v>11/16/26 – 11/22/26</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="5" t="n">
         <v>47</v>
       </c>
@@ -21757,7 +21679,7 @@
         <v>11/23/26 – 11/29/26</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="n">
         <v>48</v>
       </c>
@@ -21786,7 +21708,7 @@
         <v>11/30/26 – 12/6/26</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="5" t="n">
         <v>49</v>
       </c>
@@ -21815,7 +21737,7 @@
         <v>12/7/26 – 12/13/26</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="n">
         <v>50</v>
       </c>
@@ -21844,7 +21766,7 @@
         <v>12/14/26 – 12/20/26</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="5" t="n">
         <v>51</v>
       </c>
@@ -21873,7 +21795,7 @@
         <v>12/21/26 – 12/27/26</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="5" t="n">
         <v>52</v>
       </c>
@@ -21902,7 +21824,7 @@
         <v>12/28/26 – 1/3/27</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="5" t="n">
         <v>53</v>
       </c>
@@ -21931,7 +21853,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="n">
         <v>1</v>
       </c>
@@ -21960,7 +21882,7 @@
         <v>1/4/27 – 1/10/27</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="5" t="n">
         <v>2</v>
       </c>
@@ -21989,7 +21911,7 @@
         <v>1/11/27 – 1/17/27</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="n">
         <v>3</v>
       </c>
@@ -22018,7 +21940,7 @@
         <v>1/18/27 – 1/24/27</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="5" t="n">
         <v>4</v>
       </c>
@@ -22047,7 +21969,7 @@
         <v>1/25/27 – 1/31/27</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="n">
         <v>5</v>
       </c>
@@ -22076,7 +21998,7 @@
         <v>2/1/27 – 2/7/27</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="5" t="n">
         <v>6</v>
       </c>
@@ -22105,7 +22027,7 @@
         <v>2/8/27 – 2/14/27</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="5" t="n">
         <v>7</v>
       </c>
@@ -22134,7 +22056,7 @@
         <v>2/15/27 – 2/21/27</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="5" t="n">
         <v>8</v>
       </c>
@@ -22163,7 +22085,7 @@
         <v>2/22/27 – 2/28/27</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="5" t="n">
         <v>9</v>
       </c>
@@ -22192,7 +22114,7 @@
         <v>3/1/27 – 3/7/27</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="5" t="n">
         <v>10</v>
       </c>
@@ -22221,7 +22143,7 @@
         <v>3/8/27 – 3/14/27</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="5" t="n">
         <v>11</v>
       </c>
@@ -22250,7 +22172,7 @@
         <v>3/15/27 – 3/21/27</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="5" t="n">
         <v>12</v>
       </c>
@@ -22279,7 +22201,7 @@
         <v>3/22/27 – 3/28/27</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="n">
         <v>13</v>
       </c>
@@ -22308,7 +22230,7 @@
         <v>3/29/27 – 4/4/27</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="5" t="n">
         <v>14</v>
       </c>
@@ -22337,7 +22259,7 @@
         <v>4/5/27 – 4/11/27</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="n">
         <v>15</v>
       </c>
@@ -22366,7 +22288,7 @@
         <v>4/12/27 – 4/18/27</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="5" t="n">
         <v>16</v>
       </c>
@@ -22395,7 +22317,7 @@
         <v>4/19/27 – 4/25/27</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="5" t="n">
         <v>17</v>
       </c>
@@ -22424,7 +22346,7 @@
         <v>4/26/27 – 5/2/27</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="5" t="n">
         <v>18</v>
       </c>
@@ -22453,7 +22375,7 @@
         <v>5/3/27 – 5/9/27</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="5" t="n">
         <v>19</v>
       </c>
@@ -22482,7 +22404,7 @@
         <v>5/10/27 – 5/16/27</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="5" t="n">
         <v>20</v>
       </c>
@@ -22511,7 +22433,7 @@
         <v>5/17/27 – 5/23/27</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="5" t="n">
         <v>21</v>
       </c>
@@ -22540,7 +22462,7 @@
         <v>5/24/27 – 5/30/27</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="5" t="n">
         <v>22</v>
       </c>
@@ -22569,7 +22491,7 @@
         <v>5/31/27 – 6/6/27</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="5" t="n">
         <v>23</v>
       </c>
@@ -22598,7 +22520,7 @@
         <v>6/7/27 – 6/13/27</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="5" t="n">
         <v>24</v>
       </c>
@@ -22627,7 +22549,7 @@
         <v>6/14/27 – 6/20/27</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="5" t="n">
         <v>25</v>
       </c>
@@ -22656,7 +22578,7 @@
         <v>6/21/27 – 6/27/27</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="5" t="n">
         <v>26</v>
       </c>
@@ -22685,7 +22607,7 @@
         <v>6/28/27 – 7/4/27</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="5" t="n">
         <v>27</v>
       </c>
@@ -22714,7 +22636,7 @@
         <v>7/5/27 – 7/11/27</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="5" t="n">
         <v>28</v>
       </c>
@@ -22743,7 +22665,7 @@
         <v>7/12/27 – 7/18/27</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="n">
         <v>29</v>
       </c>
@@ -22772,7 +22694,7 @@
         <v>7/19/27 – 7/25/27</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="5" t="n">
         <v>30</v>
       </c>
@@ -22801,7 +22723,7 @@
         <v>7/26/27 – 8/1/27</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="n">
         <v>31</v>
       </c>
@@ -22830,7 +22752,7 @@
         <v>8/2/27 – 8/8/27</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="5" t="n">
         <v>32</v>
       </c>
@@ -22859,7 +22781,7 @@
         <v>8/9/27 – 8/15/27</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="n">
         <v>33</v>
       </c>
@@ -22888,7 +22810,7 @@
         <v>8/16/27 – 8/22/27</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="5" t="n">
         <v>34</v>
       </c>
@@ -22917,7 +22839,7 @@
         <v>8/23/27 – 8/29/27</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="5" t="n">
         <v>35</v>
       </c>
@@ -22973,7 +22895,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>81</v>
@@ -23012,10 +22934,10 @@
         <v>91</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="n">
         <v>45565</v>
       </c>
@@ -23051,7 +22973,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
         <v>45572</v>
       </c>
@@ -23085,7 +23007,7 @@
       </c>
       <c r="N3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
         <v>45579</v>
       </c>
@@ -23119,7 +23041,7 @@
       </c>
       <c r="N4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>45586</v>
       </c>
@@ -23153,7 +23075,7 @@
       </c>
       <c r="N5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
         <v>45593</v>
       </c>
@@ -23187,7 +23109,7 @@
       </c>
       <c r="N6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>45600</v>
       </c>
@@ -23221,7 +23143,7 @@
       </c>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>45607</v>
       </c>
@@ -23255,7 +23177,7 @@
       </c>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>45614</v>
       </c>
@@ -23291,7 +23213,7 @@
       </c>
       <c r="N9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
         <v>45621</v>
       </c>
@@ -23327,7 +23249,7 @@
       </c>
       <c r="N10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>45628</v>
       </c>
@@ -23363,7 +23285,7 @@
       </c>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>45635</v>
       </c>
@@ -23399,7 +23321,7 @@
       </c>
       <c r="N12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>45642</v>
       </c>
@@ -23435,7 +23357,7 @@
       </c>
       <c r="N13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>45649</v>
       </c>
@@ -23471,7 +23393,7 @@
       </c>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>45656</v>
       </c>
@@ -23509,7 +23431,7 @@
       </c>
       <c r="N15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>45663</v>
       </c>
@@ -23547,7 +23469,7 @@
       </c>
       <c r="N16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>45670</v>
       </c>
@@ -23585,7 +23507,7 @@
       </c>
       <c r="N17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
         <v>45677</v>
       </c>
@@ -23623,7 +23545,7 @@
       </c>
       <c r="N18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>45684</v>
       </c>
@@ -23661,7 +23583,7 @@
       </c>
       <c r="N19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
         <v>45691</v>
       </c>
@@ -23699,7 +23621,7 @@
       </c>
       <c r="N20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
         <v>45698</v>
       </c>
@@ -23737,7 +23659,7 @@
       </c>
       <c r="N21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
         <v>45705</v>
       </c>
@@ -23775,7 +23697,7 @@
       </c>
       <c r="N22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
         <v>45712</v>
       </c>
@@ -23813,7 +23735,7 @@
       </c>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
         <v>45719</v>
       </c>
@@ -23851,7 +23773,7 @@
       </c>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
         <v>45726</v>
       </c>
@@ -23889,7 +23811,7 @@
       </c>
       <c r="N25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
         <v>45733</v>
       </c>
@@ -23927,7 +23849,7 @@
       </c>
       <c r="N26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>45740</v>
       </c>
@@ -23965,7 +23887,7 @@
       </c>
       <c r="N27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
         <v>45747</v>
       </c>
@@ -24003,7 +23925,7 @@
       </c>
       <c r="N28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
         <v>45754</v>
       </c>
@@ -24041,7 +23963,7 @@
       </c>
       <c r="N29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
         <v>45761</v>
       </c>
@@ -24079,7 +24001,7 @@
       </c>
       <c r="N30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
         <v>45768</v>
       </c>
@@ -24117,7 +24039,7 @@
       </c>
       <c r="N31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
         <v>45775</v>
       </c>
@@ -24155,7 +24077,7 @@
       </c>
       <c r="N32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
         <v>45782</v>
       </c>
@@ -24193,7 +24115,7 @@
       </c>
       <c r="N33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
         <v>45789</v>
       </c>
@@ -24231,7 +24153,7 @@
       </c>
       <c r="N34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
         <v>45796</v>
       </c>
@@ -24269,7 +24191,7 @@
       </c>
       <c r="N35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
         <v>45803</v>
       </c>
@@ -24307,7 +24229,7 @@
       </c>
       <c r="N36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
         <v>45810</v>
       </c>
@@ -24345,7 +24267,7 @@
       </c>
       <c r="N37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
         <v>45817</v>
       </c>
@@ -24383,7 +24305,7 @@
       </c>
       <c r="N38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
         <v>45824</v>
       </c>
@@ -24421,7 +24343,7 @@
       </c>
       <c r="N39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
         <v>45831</v>
       </c>
@@ -24459,7 +24381,7 @@
       </c>
       <c r="N40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
         <v>45838</v>
       </c>
@@ -24497,7 +24419,7 @@
       </c>
       <c r="N41" s="7"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
         <v>45845</v>
       </c>
@@ -24535,7 +24457,7 @@
       </c>
       <c r="N42" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
         <v>45852</v>
       </c>
@@ -24573,7 +24495,7 @@
       </c>
       <c r="N43" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
         <v>45859</v>
       </c>
@@ -24611,7 +24533,7 @@
       </c>
       <c r="N44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
         <v>45866</v>
       </c>
@@ -24651,7 +24573,7 @@
       </c>
       <c r="N45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
         <v>45873</v>
       </c>
@@ -24691,7 +24613,7 @@
       </c>
       <c r="N46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
         <v>45880</v>
       </c>
@@ -24731,7 +24653,7 @@
       </c>
       <c r="N47" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
         <v>45887</v>
       </c>
@@ -24771,7 +24693,7 @@
       </c>
       <c r="N48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
         <v>45894</v>
       </c>
@@ -24811,7 +24733,7 @@
       </c>
       <c r="N49" s="7"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
         <v>45901</v>
       </c>
@@ -24851,7 +24773,7 @@
       </c>
       <c r="N50" s="7"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
         <v>45908</v>
       </c>
@@ -24891,7 +24813,7 @@
       </c>
       <c r="N51" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
         <v>45915</v>
       </c>
@@ -24931,7 +24853,7 @@
       </c>
       <c r="N52" s="7"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
         <v>45922</v>
       </c>
@@ -24971,7 +24893,7 @@
       </c>
       <c r="N53" s="7"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
         <v>45929</v>
       </c>
@@ -25011,7 +24933,7 @@
       </c>
       <c r="N54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
         <v>45936</v>
       </c>
@@ -25051,7 +24973,7 @@
       </c>
       <c r="N55" s="7"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
         <v>45943</v>
       </c>
@@ -25091,7 +25013,7 @@
       </c>
       <c r="N56" s="7"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
         <v>45950</v>
       </c>
@@ -25131,7 +25053,7 @@
       </c>
       <c r="N57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
         <v>45957</v>
       </c>
@@ -25171,7 +25093,7 @@
       </c>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
         <v>45964</v>
       </c>
@@ -25211,7 +25133,7 @@
       </c>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
         <v>45971</v>
       </c>
@@ -25251,7 +25173,7 @@
       </c>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
         <v>45978</v>
       </c>
@@ -25291,7 +25213,7 @@
       </c>
       <c r="N61" s="7"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
         <v>45985</v>
       </c>
@@ -25331,7 +25253,7 @@
       </c>
       <c r="N62" s="7"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
         <v>45992</v>
       </c>
@@ -25371,7 +25293,7 @@
       </c>
       <c r="N63" s="7"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
         <v>45999</v>
       </c>
@@ -25411,7 +25333,7 @@
       </c>
       <c r="N64" s="7"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
         <v>46006</v>
       </c>
@@ -25451,7 +25373,7 @@
       </c>
       <c r="N65" s="7"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
         <v>46013</v>
       </c>
@@ -25491,7 +25413,7 @@
       </c>
       <c r="N66" s="7"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
         <v>46020</v>
       </c>
@@ -25531,7 +25453,7 @@
       </c>
       <c r="N67" s="7"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
         <v>46027</v>
       </c>
@@ -25571,7 +25493,7 @@
       </c>
       <c r="N68" s="7"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
         <v>46034</v>
       </c>
@@ -25611,7 +25533,7 @@
       </c>
       <c r="N69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
         <v>46041</v>
       </c>
@@ -25651,7 +25573,7 @@
       </c>
       <c r="N70" s="7"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
         <v>46048</v>
       </c>
@@ -25691,7 +25613,7 @@
       </c>
       <c r="N71" s="7"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
         <v>46055</v>
       </c>
@@ -25731,7 +25653,7 @@
       </c>
       <c r="N72" s="7"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
         <v>46062</v>
       </c>
@@ -25771,7 +25693,7 @@
       </c>
       <c r="N73" s="7"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
         <v>46069</v>
       </c>
@@ -25811,7 +25733,7 @@
       </c>
       <c r="N74" s="7"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
         <v>46076</v>
       </c>
@@ -25851,7 +25773,7 @@
       </c>
       <c r="N75" s="7"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
         <v>46083</v>
       </c>
@@ -25891,7 +25813,7 @@
       </c>
       <c r="N76" s="7"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
         <v>46090</v>
       </c>
@@ -25931,7 +25853,7 @@
       </c>
       <c r="N77" s="7"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
         <v>46097</v>
       </c>
@@ -25971,7 +25893,7 @@
       </c>
       <c r="N78" s="7"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
         <v>46104</v>
       </c>
@@ -26011,7 +25933,7 @@
       </c>
       <c r="N79" s="7"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
         <v>46111</v>
       </c>
@@ -26051,7 +25973,7 @@
       </c>
       <c r="N80" s="7"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
         <v>46118</v>
       </c>
@@ -26091,7 +26013,7 @@
       </c>
       <c r="N81" s="7"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
         <v>46125</v>
       </c>
@@ -26131,7 +26053,7 @@
       </c>
       <c r="N82" s="7"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
         <v>46132</v>
       </c>
@@ -26171,7 +26093,7 @@
       </c>
       <c r="N83" s="7"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="n">
         <v>46139</v>
       </c>
@@ -26211,7 +26133,7 @@
       </c>
       <c r="N84" s="7"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="n">
         <v>46146</v>
       </c>
@@ -26251,7 +26173,7 @@
       </c>
       <c r="N85" s="7"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="n">
         <v>46153</v>
       </c>
@@ -26291,7 +26213,7 @@
       </c>
       <c r="N86" s="7"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="n">
         <v>46160</v>
       </c>
@@ -26331,7 +26253,7 @@
       </c>
       <c r="N87" s="7"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="n">
         <v>46167</v>
       </c>
@@ -26371,7 +26293,7 @@
       </c>
       <c r="N88" s="7"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="n">
         <v>46174</v>
       </c>
@@ -26411,7 +26333,7 @@
       </c>
       <c r="N89" s="7"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="n">
         <v>46181</v>
       </c>
@@ -26451,7 +26373,7 @@
       </c>
       <c r="N90" s="7"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="n">
         <v>46188</v>
       </c>
@@ -26491,7 +26413,7 @@
       </c>
       <c r="N91" s="7"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="n">
         <v>46195</v>
       </c>
@@ -26531,7 +26453,7 @@
       </c>
       <c r="N92" s="7"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="n">
         <v>46202</v>
       </c>
@@ -26571,7 +26493,7 @@
       </c>
       <c r="N93" s="7"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="n">
         <v>46209</v>
       </c>
@@ -26611,7 +26533,7 @@
       </c>
       <c r="N94" s="7"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="n">
         <v>46216</v>
       </c>
@@ -26651,7 +26573,7 @@
       </c>
       <c r="N95" s="7"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="n">
         <v>46223</v>
       </c>
@@ -26691,7 +26613,7 @@
       </c>
       <c r="N96" s="7"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="n">
         <v>46230</v>
       </c>
@@ -26731,7 +26653,7 @@
       </c>
       <c r="N97" s="7"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="n">
         <v>46237</v>
       </c>
@@ -26771,7 +26693,7 @@
       </c>
       <c r="N98" s="7"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="n">
         <v>46244</v>
       </c>
@@ -26811,7 +26733,7 @@
       </c>
       <c r="N99" s="7"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="n">
         <v>46251</v>
       </c>
@@ -26851,7 +26773,7 @@
       </c>
       <c r="N100" s="7"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="n">
         <v>46258</v>
       </c>
@@ -26891,7 +26813,7 @@
       </c>
       <c r="N101" s="7"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="n">
         <v>46265</v>
       </c>
@@ -26931,7 +26853,7 @@
       </c>
       <c r="N102" s="7"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="n">
         <v>46272</v>
       </c>
@@ -26999,7 +26921,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>81</v>
@@ -27017,10 +26939,10 @@
         <v>84</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="n">
         <v>46272</v>
       </c>
@@ -27031,7 +26953,7 @@
       <c r="F2" s="6"/>
       <c r="G2" s="7"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
         <v>46279</v>
       </c>
@@ -27042,7 +26964,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
         <v>46286</v>
       </c>
@@ -27053,7 +26975,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>46293</v>
       </c>
@@ -27064,7 +26986,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
         <v>46300</v>
       </c>
@@ -27075,7 +26997,7 @@
       <c r="F6" s="6"/>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>46307</v>
       </c>
@@ -27086,18 +27008,30 @@
       <c r="F7" s="6"/>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="n">
+        <v>213.41</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>46321</v>
       </c>
@@ -27108,7 +27042,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
         <v>46328</v>
       </c>
@@ -27119,7 +27053,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>46335</v>
       </c>
@@ -27130,7 +27064,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>46342</v>
       </c>
@@ -27141,7 +27075,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>46349</v>
       </c>
@@ -27152,7 +27086,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>46356</v>
       </c>
@@ -27163,7 +27097,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>46363</v>
       </c>
@@ -27174,7 +27108,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>46370</v>
       </c>
@@ -27185,7 +27119,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>46377</v>
       </c>
@@ -27196,7 +27130,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
         <v>46384</v>
       </c>
@@ -27207,7 +27141,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>46391</v>
       </c>
@@ -27218,7 +27152,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
         <v>46398</v>
       </c>
@@ -27229,7 +27163,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
         <v>46405</v>
       </c>
@@ -27240,7 +27174,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
         <v>46412</v>
       </c>
@@ -27251,7 +27185,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
         <v>46419</v>
       </c>
@@ -27262,7 +27196,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
         <v>46426</v>
       </c>
@@ -27273,7 +27207,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
         <v>46433</v>
       </c>
@@ -27284,7 +27218,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
         <v>46440</v>
       </c>
@@ -27295,7 +27229,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>46447</v>
       </c>
@@ -27306,7 +27240,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
         <v>46454</v>
       </c>
@@ -27317,7 +27251,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
         <v>46461</v>
       </c>
@@ -27328,7 +27262,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
         <v>46468</v>
       </c>
@@ -27339,7 +27273,7 @@
       <c r="F30" s="6"/>
       <c r="G30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
         <v>46475</v>
       </c>
@@ -27350,7 +27284,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
         <v>46482</v>
       </c>
@@ -27361,7 +27295,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
         <v>46489</v>
       </c>
@@ -27372,7 +27306,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
         <v>46496</v>
       </c>
@@ -27383,7 +27317,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
         <v>46503</v>
       </c>
@@ -27394,7 +27328,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
         <v>46510</v>
       </c>
@@ -27405,7 +27339,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
         <v>46517</v>
       </c>
@@ -27416,7 +27350,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
         <v>46524</v>
       </c>
@@ -27427,7 +27361,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
         <v>46531</v>
       </c>
@@ -27438,7 +27372,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
         <v>46538</v>
       </c>
@@ -27449,150 +27383,108 @@
       <c r="F40" s="6"/>
       <c r="G40" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
         <v>81</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>-0.398</v>
-      </c>
-      <c r="D45" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E45" s="8" t="n">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="8"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="B47" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E46" s="8" t="n">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+      <c r="B48" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="8"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="B49" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
         <v>82</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="8"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
         <v>83</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="8"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -27634,37 +27526,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="J1" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="n">
         <v>46272</v>
       </c>
@@ -27684,7 +27576,7 @@
       <c r="I2" s="15"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
         <v>46279</v>
       </c>
@@ -27704,7 +27596,7 @@
       <c r="I3" s="15"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
         <v>46286</v>
       </c>
@@ -27724,7 +27616,7 @@
       <c r="I4" s="15"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>46293</v>
       </c>
@@ -27738,7 +27630,7 @@
         <v>4.4E-005</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="15"/>
@@ -27746,7 +27638,7 @@
       <c r="I5" s="15"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
         <v>46300</v>
       </c>
@@ -27760,7 +27652,7 @@
         <v>0.005</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="15"/>
@@ -27768,35 +27660,51 @@
       <c r="I6" s="15"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>46307</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="6"/>
+      <c r="B7" s="15" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>113</v>
+      </c>
       <c r="F7" s="6"/>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="6"/>
+      <c r="B8" s="15" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>113</v>
+      </c>
       <c r="F8" s="6"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>46321</v>
       </c>
@@ -27810,7 +27718,7 @@
       <c r="I9" s="15"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
         <v>46328</v>
       </c>
@@ -27824,7 +27732,7 @@
       <c r="I10" s="15"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>46335</v>
       </c>
@@ -27838,7 +27746,7 @@
       <c r="I11" s="15"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>46342</v>
       </c>
@@ -27852,7 +27760,7 @@
       <c r="I12" s="15"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>46349</v>
       </c>
@@ -27866,7 +27774,7 @@
       <c r="I13" s="15"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>46356</v>
       </c>
@@ -27880,7 +27788,7 @@
       <c r="I14" s="15"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>46363</v>
       </c>
@@ -27894,7 +27802,7 @@
       <c r="I15" s="15"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>46370</v>
       </c>
@@ -27908,7 +27816,7 @@
       <c r="I16" s="15"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>46377</v>
       </c>
@@ -27922,7 +27830,7 @@
       <c r="I17" s="15"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
         <v>46384</v>
       </c>
@@ -27936,7 +27844,7 @@
       <c r="I18" s="15"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>46391</v>
       </c>
@@ -27950,7 +27858,7 @@
       <c r="I19" s="15"/>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
         <v>46398</v>
       </c>
@@ -27964,7 +27872,7 @@
       <c r="I20" s="15"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
         <v>46405</v>
       </c>
@@ -27978,7 +27886,7 @@
       <c r="I21" s="15"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
         <v>46412</v>
       </c>
@@ -27992,7 +27900,7 @@
       <c r="I22" s="15"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
         <v>46419</v>
       </c>
@@ -28006,7 +27914,7 @@
       <c r="I23" s="15"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
         <v>46426</v>
       </c>
@@ -28020,7 +27928,7 @@
       <c r="I24" s="15"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
         <v>46433</v>
       </c>
@@ -28034,7 +27942,7 @@
       <c r="I25" s="15"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
         <v>46440</v>
       </c>
@@ -28048,7 +27956,7 @@
       <c r="I26" s="15"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>46447</v>
       </c>
@@ -28062,7 +27970,7 @@
       <c r="I27" s="15"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
         <v>46454</v>
       </c>
@@ -28076,7 +27984,7 @@
       <c r="I28" s="15"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
         <v>46461</v>
       </c>
@@ -28090,7 +27998,7 @@
       <c r="I29" s="15"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
         <v>46468</v>
       </c>
@@ -28104,7 +28012,7 @@
       <c r="I30" s="15"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
         <v>46475</v>
       </c>
@@ -28118,7 +28026,7 @@
       <c r="I31" s="15"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
         <v>46482</v>
       </c>
@@ -28132,7 +28040,7 @@
       <c r="I32" s="15"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
         <v>46489</v>
       </c>
@@ -28146,7 +28054,7 @@
       <c r="I33" s="15"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
         <v>46496</v>
       </c>
@@ -28160,7 +28068,7 @@
       <c r="I34" s="15"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
         <v>46503</v>
       </c>
@@ -28174,7 +28082,7 @@
       <c r="I35" s="15"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
         <v>46510</v>
       </c>
@@ -28188,7 +28096,7 @@
       <c r="I36" s="15"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
         <v>46517</v>
       </c>
@@ -28202,7 +28110,7 @@
       <c r="I37" s="15"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
         <v>46524</v>
       </c>
@@ -28216,7 +28124,7 @@
       <c r="I38" s="15"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
         <v>46531</v>
       </c>
@@ -28230,7 +28138,7 @@
       <c r="I39" s="15"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
         <v>46538</v>
       </c>
@@ -28244,9 +28152,9 @@
       <c r="I40" s="15"/>
       <c r="J40" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -28275,261 +28183,141 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D1" s="4" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="C3" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="4" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="4" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <f aca="false">SUM(C2:E2)</f>
-        <v>7</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <f aca="false">IF(F2=0,"",D2/F2)</f>
-        <v>0.285714285714286</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C7" s="18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <f aca="false">SUM(C3:E3)</f>
-        <v>5</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <f aca="false">IF(F3=0,"",D3/F3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="C8" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <f aca="false">SUM(C4:E4)</f>
-        <v>5</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <f aca="false">IF(F4=0,"",D4/F4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <f aca="false">SUM(C5:E5)</f>
-        <v>3</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <f aca="false">IF(F5=0,"",D5/F5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="6" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <f aca="false">SUM(C6:E6)</f>
-        <v>1</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <f aca="false">IF(F6=0,"",D6/F6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="5" t="n">
-        <f aca="false">SUM(C7:E7)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="10" t="str">
-        <f aca="false">IF(F7=0,"",D7/F7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="5" t="n">
-        <f aca="false">SUM(C8:E8)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="10" t="str">
-        <f aca="false">IF(F8=0,"",D8/F8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="5" t="n">
-        <f aca="false">SUM(C9:E9)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="10" t="str">
-        <f aca="false">IF(F9=0,"",D9/F9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="5" t="n">
-        <f aca="false">SUM(C10:E10)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="10" t="str">
-        <f aca="false">IF(F10=0,"",D10/F10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="5" t="n">
-        <f aca="false">SUM(C11:E11)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="10" t="str">
-        <f aca="false">IF(F11=0,"",D11/F11)</f>
-        <v/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C7" r:id="rId1" display="https://www.cdph.ca.gov/Programs/CID/DCDC/Pages/RespiratoryVirusReport.aspx"/>
+    <hyperlink ref="C8" r:id="rId2" display="https://www.cdph.ca.gov/Programs/CID/DCDC/Pages/Respiratory-Viruses/Home.aspx"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -28537,6 +28325,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/respiratory/RV_Tracker.xlsx
+++ b/respiratory/RV_Tracker.xlsx
@@ -689,7 +689,7 @@
     <row r="7" ht="15" customHeight="1" s="20">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>3. Wastewater_Local: enter Verily values for the Mammoth plant and the current UC Davis trend table. These also feed the Cases vs wastewater tab.</t>
+          <t>3. Wastewater_Local: enter Verily values for the Mammoth plant (SARS-CoV-2, influenza A and B, RSV, H5, H1, H3, measles; weekly mean of virus ÷ PMMoV × 1,000,000) and the current UC Davis trend table. These also feed the Cases vs wastewater tab. Mpox is no longer tested under the new contract.</t>
         </is>
       </c>
     </row>
@@ -26782,13 +26782,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="19" min="1" max="4"/>
     <col width="10" customWidth="1" style="19" min="5" max="5"/>
     <col width="16" customWidth="1" style="19" min="6" max="6"/>
-    <col width="60" customWidth="1" style="19" min="7" max="7"/>
+    <col width="16" customWidth="1" style="19" min="7" max="7"/>
+    <col width="16" customWidth="1" style="20" min="8" max="8"/>
+    <col width="16" customWidth="1" style="20" min="9" max="9"/>
+    <col width="60" customWidth="1" style="20" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1" s="20">
@@ -26824,6 +26827,21 @@
       </c>
       <c r="G1" s="24" t="inlineStr">
         <is>
+          <t>Influenza A (H1)</t>
+        </is>
+      </c>
+      <c r="H1" s="24" t="inlineStr">
+        <is>
+          <t>Influenza A (H3)</t>
+        </is>
+      </c>
+      <c r="I1" s="24" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J1" s="24" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -26837,7 +26855,10 @@
       <c r="D2" s="26" t="n"/>
       <c r="E2" s="26" t="n"/>
       <c r="F2" s="26" t="n"/>
-      <c r="G2" s="27" t="n"/>
+      <c r="G2" s="26" t="n"/>
+      <c r="H2" s="26" t="n"/>
+      <c r="I2" s="26" t="n"/>
+      <c r="J2" s="27" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="20">
       <c r="A3" s="28" t="n">
@@ -26848,7 +26869,10 @@
       <c r="D3" s="26" t="n"/>
       <c r="E3" s="26" t="n"/>
       <c r="F3" s="26" t="n"/>
-      <c r="G3" s="27" t="n"/>
+      <c r="G3" s="26" t="n"/>
+      <c r="H3" s="26" t="n"/>
+      <c r="I3" s="26" t="n"/>
+      <c r="J3" s="27" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="20">
       <c r="A4" s="28" t="n">
@@ -26859,7 +26883,10 @@
       <c r="D4" s="26" t="n"/>
       <c r="E4" s="26" t="n"/>
       <c r="F4" s="26" t="n"/>
-      <c r="G4" s="27" t="n"/>
+      <c r="G4" s="26" t="n"/>
+      <c r="H4" s="26" t="n"/>
+      <c r="I4" s="26" t="n"/>
+      <c r="J4" s="27" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="20">
       <c r="A5" s="28" t="n">
@@ -26870,7 +26897,10 @@
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="26" t="n"/>
-      <c r="G5" s="27" t="n"/>
+      <c r="G5" s="26" t="n"/>
+      <c r="H5" s="26" t="n"/>
+      <c r="I5" s="26" t="n"/>
+      <c r="J5" s="27" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="20">
       <c r="A6" s="28" t="n">
@@ -26881,7 +26911,10 @@
       <c r="D6" s="26" t="n"/>
       <c r="E6" s="26" t="n"/>
       <c r="F6" s="26" t="n"/>
-      <c r="G6" s="27" t="n"/>
+      <c r="G6" s="26" t="n"/>
+      <c r="H6" s="26" t="n"/>
+      <c r="I6" s="26" t="n"/>
+      <c r="J6" s="27" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
       <c r="A7" s="28" t="n">
@@ -26892,7 +26925,10 @@
       <c r="D7" s="26" t="n"/>
       <c r="E7" s="26" t="n"/>
       <c r="F7" s="26" t="n"/>
-      <c r="G7" s="27" t="n"/>
+      <c r="G7" s="26" t="n"/>
+      <c r="H7" s="26" t="n"/>
+      <c r="I7" s="26" t="n"/>
+      <c r="J7" s="27" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="20">
       <c r="A8" s="28" t="n">
@@ -26913,9 +26949,18 @@
       <c r="F8" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="26" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="27" t="inlineStr">
         <is>
-          <t>1 sample (10/21), first under new contract. Influenza A H1 subtype detected at 4.02.</t>
+          <t>1 sample (10/21), first under new contract.</t>
         </is>
       </c>
     </row>
@@ -26928,7 +26973,10 @@
       <c r="D9" s="26" t="n"/>
       <c r="E9" s="26" t="n"/>
       <c r="F9" s="26" t="n"/>
-      <c r="G9" s="27" t="n"/>
+      <c r="G9" s="26" t="n"/>
+      <c r="H9" s="26" t="n"/>
+      <c r="I9" s="26" t="n"/>
+      <c r="J9" s="27" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="20">
       <c r="A10" s="28" t="n">
@@ -26939,7 +26987,10 @@
       <c r="D10" s="26" t="n"/>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="26" t="n"/>
-      <c r="G10" s="27" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="26" t="n"/>
+      <c r="I10" s="26" t="n"/>
+      <c r="J10" s="27" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="20">
       <c r="A11" s="28" t="n">
@@ -26950,7 +27001,10 @@
       <c r="D11" s="26" t="n"/>
       <c r="E11" s="26" t="n"/>
       <c r="F11" s="26" t="n"/>
-      <c r="G11" s="27" t="n"/>
+      <c r="G11" s="26" t="n"/>
+      <c r="H11" s="26" t="n"/>
+      <c r="I11" s="26" t="n"/>
+      <c r="J11" s="27" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="20">
       <c r="A12" s="28" t="n">
@@ -26961,7 +27015,10 @@
       <c r="D12" s="26" t="n"/>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="26" t="n"/>
-      <c r="G12" s="27" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="26" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="27" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="20">
       <c r="A13" s="28" t="n">
@@ -26972,7 +27029,10 @@
       <c r="D13" s="26" t="n"/>
       <c r="E13" s="26" t="n"/>
       <c r="F13" s="26" t="n"/>
-      <c r="G13" s="27" t="n"/>
+      <c r="G13" s="26" t="n"/>
+      <c r="H13" s="26" t="n"/>
+      <c r="I13" s="26" t="n"/>
+      <c r="J13" s="27" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="20">
       <c r="A14" s="28" t="n">
@@ -26983,7 +27043,10 @@
       <c r="D14" s="26" t="n"/>
       <c r="E14" s="26" t="n"/>
       <c r="F14" s="26" t="n"/>
-      <c r="G14" s="27" t="n"/>
+      <c r="G14" s="26" t="n"/>
+      <c r="H14" s="26" t="n"/>
+      <c r="I14" s="26" t="n"/>
+      <c r="J14" s="27" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="20">
       <c r="A15" s="28" t="n">
@@ -26994,7 +27057,10 @@
       <c r="D15" s="26" t="n"/>
       <c r="E15" s="26" t="n"/>
       <c r="F15" s="26" t="n"/>
-      <c r="G15" s="27" t="n"/>
+      <c r="G15" s="26" t="n"/>
+      <c r="H15" s="26" t="n"/>
+      <c r="I15" s="26" t="n"/>
+      <c r="J15" s="27" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="20">
       <c r="A16" s="28" t="n">
@@ -27005,7 +27071,10 @@
       <c r="D16" s="26" t="n"/>
       <c r="E16" s="26" t="n"/>
       <c r="F16" s="26" t="n"/>
-      <c r="G16" s="27" t="n"/>
+      <c r="G16" s="26" t="n"/>
+      <c r="H16" s="26" t="n"/>
+      <c r="I16" s="26" t="n"/>
+      <c r="J16" s="27" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="20">
       <c r="A17" s="28" t="n">
@@ -27016,7 +27085,10 @@
       <c r="D17" s="26" t="n"/>
       <c r="E17" s="26" t="n"/>
       <c r="F17" s="26" t="n"/>
-      <c r="G17" s="27" t="n"/>
+      <c r="G17" s="26" t="n"/>
+      <c r="H17" s="26" t="n"/>
+      <c r="I17" s="26" t="n"/>
+      <c r="J17" s="27" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="20">
       <c r="A18" s="28" t="n">
@@ -27027,7 +27099,10 @@
       <c r="D18" s="26" t="n"/>
       <c r="E18" s="26" t="n"/>
       <c r="F18" s="26" t="n"/>
-      <c r="G18" s="27" t="n"/>
+      <c r="G18" s="26" t="n"/>
+      <c r="H18" s="26" t="n"/>
+      <c r="I18" s="26" t="n"/>
+      <c r="J18" s="27" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="20">
       <c r="A19" s="28" t="n">
@@ -27038,7 +27113,10 @@
       <c r="D19" s="26" t="n"/>
       <c r="E19" s="26" t="n"/>
       <c r="F19" s="26" t="n"/>
-      <c r="G19" s="27" t="n"/>
+      <c r="G19" s="26" t="n"/>
+      <c r="H19" s="26" t="n"/>
+      <c r="I19" s="26" t="n"/>
+      <c r="J19" s="27" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="20">
       <c r="A20" s="28" t="n">
@@ -27049,7 +27127,10 @@
       <c r="D20" s="26" t="n"/>
       <c r="E20" s="26" t="n"/>
       <c r="F20" s="26" t="n"/>
-      <c r="G20" s="27" t="n"/>
+      <c r="G20" s="26" t="n"/>
+      <c r="H20" s="26" t="n"/>
+      <c r="I20" s="26" t="n"/>
+      <c r="J20" s="27" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="20">
       <c r="A21" s="28" t="n">
@@ -27060,7 +27141,10 @@
       <c r="D21" s="26" t="n"/>
       <c r="E21" s="26" t="n"/>
       <c r="F21" s="26" t="n"/>
-      <c r="G21" s="27" t="n"/>
+      <c r="G21" s="26" t="n"/>
+      <c r="H21" s="26" t="n"/>
+      <c r="I21" s="26" t="n"/>
+      <c r="J21" s="27" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="20">
       <c r="A22" s="28" t="n">
@@ -27071,7 +27155,10 @@
       <c r="D22" s="26" t="n"/>
       <c r="E22" s="26" t="n"/>
       <c r="F22" s="26" t="n"/>
-      <c r="G22" s="27" t="n"/>
+      <c r="G22" s="26" t="n"/>
+      <c r="H22" s="26" t="n"/>
+      <c r="I22" s="26" t="n"/>
+      <c r="J22" s="27" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="20">
       <c r="A23" s="28" t="n">
@@ -27082,7 +27169,10 @@
       <c r="D23" s="26" t="n"/>
       <c r="E23" s="26" t="n"/>
       <c r="F23" s="26" t="n"/>
-      <c r="G23" s="27" t="n"/>
+      <c r="G23" s="26" t="n"/>
+      <c r="H23" s="26" t="n"/>
+      <c r="I23" s="26" t="n"/>
+      <c r="J23" s="27" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="20">
       <c r="A24" s="28" t="n">
@@ -27093,7 +27183,10 @@
       <c r="D24" s="26" t="n"/>
       <c r="E24" s="26" t="n"/>
       <c r="F24" s="26" t="n"/>
-      <c r="G24" s="27" t="n"/>
+      <c r="G24" s="26" t="n"/>
+      <c r="H24" s="26" t="n"/>
+      <c r="I24" s="26" t="n"/>
+      <c r="J24" s="27" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="20">
       <c r="A25" s="28" t="n">
@@ -27104,7 +27197,10 @@
       <c r="D25" s="26" t="n"/>
       <c r="E25" s="26" t="n"/>
       <c r="F25" s="26" t="n"/>
-      <c r="G25" s="27" t="n"/>
+      <c r="G25" s="26" t="n"/>
+      <c r="H25" s="26" t="n"/>
+      <c r="I25" s="26" t="n"/>
+      <c r="J25" s="27" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="20">
       <c r="A26" s="28" t="n">
@@ -27115,7 +27211,10 @@
       <c r="D26" s="26" t="n"/>
       <c r="E26" s="26" t="n"/>
       <c r="F26" s="26" t="n"/>
-      <c r="G26" s="27" t="n"/>
+      <c r="G26" s="26" t="n"/>
+      <c r="H26" s="26" t="n"/>
+      <c r="I26" s="26" t="n"/>
+      <c r="J26" s="27" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="20">
       <c r="A27" s="28" t="n">
@@ -27126,7 +27225,10 @@
       <c r="D27" s="26" t="n"/>
       <c r="E27" s="26" t="n"/>
       <c r="F27" s="26" t="n"/>
-      <c r="G27" s="27" t="n"/>
+      <c r="G27" s="26" t="n"/>
+      <c r="H27" s="26" t="n"/>
+      <c r="I27" s="26" t="n"/>
+      <c r="J27" s="27" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="20">
       <c r="A28" s="28" t="n">
@@ -27137,7 +27239,10 @@
       <c r="D28" s="26" t="n"/>
       <c r="E28" s="26" t="n"/>
       <c r="F28" s="26" t="n"/>
-      <c r="G28" s="27" t="n"/>
+      <c r="G28" s="26" t="n"/>
+      <c r="H28" s="26" t="n"/>
+      <c r="I28" s="26" t="n"/>
+      <c r="J28" s="27" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="20">
       <c r="A29" s="28" t="n">
@@ -27148,7 +27253,10 @@
       <c r="D29" s="26" t="n"/>
       <c r="E29" s="26" t="n"/>
       <c r="F29" s="26" t="n"/>
-      <c r="G29" s="27" t="n"/>
+      <c r="G29" s="26" t="n"/>
+      <c r="H29" s="26" t="n"/>
+      <c r="I29" s="26" t="n"/>
+      <c r="J29" s="27" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="20">
       <c r="A30" s="28" t="n">
@@ -27159,7 +27267,10 @@
       <c r="D30" s="26" t="n"/>
       <c r="E30" s="26" t="n"/>
       <c r="F30" s="26" t="n"/>
-      <c r="G30" s="27" t="n"/>
+      <c r="G30" s="26" t="n"/>
+      <c r="H30" s="26" t="n"/>
+      <c r="I30" s="26" t="n"/>
+      <c r="J30" s="27" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="20">
       <c r="A31" s="28" t="n">
@@ -27170,7 +27281,10 @@
       <c r="D31" s="26" t="n"/>
       <c r="E31" s="26" t="n"/>
       <c r="F31" s="26" t="n"/>
-      <c r="G31" s="27" t="n"/>
+      <c r="G31" s="26" t="n"/>
+      <c r="H31" s="26" t="n"/>
+      <c r="I31" s="26" t="n"/>
+      <c r="J31" s="27" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="20">
       <c r="A32" s="28" t="n">
@@ -27181,7 +27295,10 @@
       <c r="D32" s="26" t="n"/>
       <c r="E32" s="26" t="n"/>
       <c r="F32" s="26" t="n"/>
-      <c r="G32" s="27" t="n"/>
+      <c r="G32" s="26" t="n"/>
+      <c r="H32" s="26" t="n"/>
+      <c r="I32" s="26" t="n"/>
+      <c r="J32" s="27" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="20">
       <c r="A33" s="28" t="n">
@@ -27192,7 +27309,10 @@
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="26" t="n"/>
       <c r="F33" s="26" t="n"/>
-      <c r="G33" s="27" t="n"/>
+      <c r="G33" s="26" t="n"/>
+      <c r="H33" s="26" t="n"/>
+      <c r="I33" s="26" t="n"/>
+      <c r="J33" s="27" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="20">
       <c r="A34" s="28" t="n">
@@ -27203,7 +27323,10 @@
       <c r="D34" s="26" t="n"/>
       <c r="E34" s="26" t="n"/>
       <c r="F34" s="26" t="n"/>
-      <c r="G34" s="27" t="n"/>
+      <c r="G34" s="26" t="n"/>
+      <c r="H34" s="26" t="n"/>
+      <c r="I34" s="26" t="n"/>
+      <c r="J34" s="27" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="20">
       <c r="A35" s="28" t="n">
@@ -27214,7 +27337,10 @@
       <c r="D35" s="26" t="n"/>
       <c r="E35" s="26" t="n"/>
       <c r="F35" s="26" t="n"/>
-      <c r="G35" s="27" t="n"/>
+      <c r="G35" s="26" t="n"/>
+      <c r="H35" s="26" t="n"/>
+      <c r="I35" s="26" t="n"/>
+      <c r="J35" s="27" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="20">
       <c r="A36" s="28" t="n">
@@ -27225,7 +27351,10 @@
       <c r="D36" s="26" t="n"/>
       <c r="E36" s="26" t="n"/>
       <c r="F36" s="26" t="n"/>
-      <c r="G36" s="27" t="n"/>
+      <c r="G36" s="26" t="n"/>
+      <c r="H36" s="26" t="n"/>
+      <c r="I36" s="26" t="n"/>
+      <c r="J36" s="27" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="20">
       <c r="A37" s="28" t="n">
@@ -27236,7 +27365,10 @@
       <c r="D37" s="26" t="n"/>
       <c r="E37" s="26" t="n"/>
       <c r="F37" s="26" t="n"/>
-      <c r="G37" s="27" t="n"/>
+      <c r="G37" s="26" t="n"/>
+      <c r="H37" s="26" t="n"/>
+      <c r="I37" s="26" t="n"/>
+      <c r="J37" s="27" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="20">
       <c r="A38" s="28" t="n">
@@ -27247,7 +27379,10 @@
       <c r="D38" s="26" t="n"/>
       <c r="E38" s="26" t="n"/>
       <c r="F38" s="26" t="n"/>
-      <c r="G38" s="27" t="n"/>
+      <c r="G38" s="26" t="n"/>
+      <c r="H38" s="26" t="n"/>
+      <c r="I38" s="26" t="n"/>
+      <c r="J38" s="27" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="20">
       <c r="A39" s="28" t="n">
@@ -27258,7 +27393,10 @@
       <c r="D39" s="26" t="n"/>
       <c r="E39" s="26" t="n"/>
       <c r="F39" s="26" t="n"/>
-      <c r="G39" s="27" t="n"/>
+      <c r="G39" s="26" t="n"/>
+      <c r="H39" s="26" t="n"/>
+      <c r="I39" s="26" t="n"/>
+      <c r="J39" s="27" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="20">
       <c r="A40" s="28" t="n">
@@ -27269,8 +27407,13 @@
       <c r="D40" s="26" t="n"/>
       <c r="E40" s="26" t="n"/>
       <c r="F40" s="26" t="n"/>
-      <c r="G40" s="27" t="n"/>
-    </row>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="26" t="n"/>
+      <c r="I40" s="26" t="n"/>
+      <c r="J40" s="27" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43" ht="15" customHeight="1" s="20">
       <c r="A43" s="34" t="inlineStr">
         <is>
@@ -28207,7 +28350,7 @@
           <t>**Covid-19 cases ↓ this week.** Mono County reported 1 Covid-19 case, 0 flu cases, and 0 RSV cases for 10/5–10/11. Season-to-date since 9/7: 18 Covid-19, 1 flu, 1 RSV.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>Mono County cases</t>
         </is>
@@ -28222,7 +28365,7 @@
           <t>**Covid-19 positivity ↓ 14%** (1 of 7 tests), down from 31% the prior week. All 11 flu tests and all 11 RSV tests were negative.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Test positivity</t>
         </is>
@@ -28237,7 +28380,7 @@
           <t>**2 flu patients, both influenza A**, neither a Mono County resident. No Covid-19 or RSV patients. Local wastewater sampling paused since 9/9.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Mammoth Hospital</t>
         </is>
@@ -28292,7 +28435,7 @@
           <t>**Fewer local cases this week.** Mono County reported 1 Covid-19 case (↓ from 6), 3 flu cases (↓ from 7), and 1 RSV case for 10/19–10/25. Season-to-date since 9/7: 25 Covid-19, 11 flu, 2 RSV.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Mono County cases</t>
         </is>
@@ -28307,7 +28450,7 @@
           <t>**Flu positivity ↓ 23%** (3 of 13 tests), down from 33% the prior week. Covid-19 ↓ 10% (1 of 10), down from 50%. RSV 8% (1 of 12).</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>Test positivity</t>
         </is>
@@ -28322,7 +28465,7 @@
           <t>**4 flu patients, mostly influenza A** (3 A, 1 B). 3 were Mono County residents; 2 of the 4 were vaccinated. 1 RSV patient (not a Mono County resident); no Covid-19 patients.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Mammoth Hospital</t>
         </is>
@@ -28337,7 +28480,7 @@
           <t>**Local sampling resumed 10/21.** SARS-CoV-2 detected at a level similar to early September. Influenza A, influenza B, and RSV not detected; the influenza A H1 subtype was detected at a low level. UC Davis trends return once more samples are collected.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Wastewater</t>
         </is>
